--- a/DAT/raw/data_BodyPerception_new.xlsx
+++ b/DAT/raw/data_BodyPerception_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/delphinehund/Desktop/Stage/Projet 1 Weight Stigma/Pré-manip/V2/code/DAT/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EE415F-D676-D446-8307-6191D2492C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7E1F36-47B5-CD4A-91B8-0DF740D67EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="8880" windowWidth="16380" windowHeight="16520" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11760" yWindow="1160" windowWidth="16380" windowHeight="16520" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BodyPerception" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="504">
   <si>
     <t>CASE</t>
   </si>
@@ -1487,6 +1487,51 @@
   </si>
   <si>
     <t>50</t>
+  </si>
+  <si>
+    <t>Gaetan Vergnon</t>
+  </si>
+  <si>
+    <t>05/03/2001</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Hund Sébastien</t>
+  </si>
+  <si>
+    <t>11-09/2000</t>
+  </si>
+  <si>
+    <t>HUSE</t>
+  </si>
+  <si>
+    <t>Dubief</t>
+  </si>
+  <si>
+    <t>22/11/2001</t>
+  </si>
+  <si>
+    <t>DUBL</t>
+  </si>
+  <si>
+    <t>Jocelyn Precloux</t>
+  </si>
+  <si>
+    <t>06/03/1970</t>
+  </si>
+  <si>
+    <t>PRJO</t>
+  </si>
+  <si>
+    <t>56</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:KQ16"/>
+  <dimension ref="A1:KQ20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -9627,6 +9672,1698 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="17" spans="1:303" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>948</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F17" s="3">
+        <v>46097.738518519</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="P17" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="1">
+        <v>33</v>
+      </c>
+      <c r="V17" s="1">
+        <v>63</v>
+      </c>
+      <c r="W17" s="1">
+        <v>63</v>
+      </c>
+      <c r="X17" s="1">
+        <v>50</v>
+      </c>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1">
+        <v>8</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>62</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>51</v>
+      </c>
+      <c r="AJ17" s="1">
+        <v>37</v>
+      </c>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+      <c r="AP17" s="1"/>
+      <c r="AQ17" s="1"/>
+      <c r="AR17" s="1"/>
+      <c r="AS17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="1">
+        <v>24</v>
+      </c>
+      <c r="AV17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW17" s="1"/>
+      <c r="AX17" s="1"/>
+      <c r="AY17" s="1"/>
+      <c r="AZ17" s="1"/>
+      <c r="BA17" s="1"/>
+      <c r="BB17" s="1"/>
+      <c r="BC17" s="1"/>
+      <c r="BD17" s="1"/>
+      <c r="BE17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BF17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BH17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BI17" s="1"/>
+      <c r="BJ17" s="1"/>
+      <c r="BK17" s="1"/>
+      <c r="BL17" s="1"/>
+      <c r="BM17" s="1"/>
+      <c r="BN17" s="1"/>
+      <c r="BO17" s="1"/>
+      <c r="BP17" s="1"/>
+      <c r="BQ17" s="1">
+        <v>91</v>
+      </c>
+      <c r="BR17" s="1">
+        <v>68</v>
+      </c>
+      <c r="BS17" s="1">
+        <v>23</v>
+      </c>
+      <c r="BT17" s="1">
+        <v>83</v>
+      </c>
+      <c r="BU17" s="1"/>
+      <c r="BV17" s="1"/>
+      <c r="BW17" s="1"/>
+      <c r="BX17" s="1"/>
+      <c r="BY17" s="1"/>
+      <c r="BZ17" s="1"/>
+      <c r="CA17" s="1"/>
+      <c r="CB17" s="1"/>
+      <c r="CC17" s="1">
+        <v>89</v>
+      </c>
+      <c r="CD17" s="1">
+        <v>38</v>
+      </c>
+      <c r="CE17" s="1">
+        <v>1</v>
+      </c>
+      <c r="CF17" s="1">
+        <v>101</v>
+      </c>
+      <c r="CG17" s="1"/>
+      <c r="CH17" s="1"/>
+      <c r="CI17" s="1"/>
+      <c r="CJ17" s="1"/>
+      <c r="CK17" s="1"/>
+      <c r="CL17" s="1"/>
+      <c r="CM17" s="1"/>
+      <c r="CN17" s="1"/>
+      <c r="CO17" s="1"/>
+      <c r="CP17" s="1"/>
+      <c r="CQ17" s="1"/>
+      <c r="CR17" s="1"/>
+      <c r="CS17" s="1"/>
+      <c r="CT17" s="1"/>
+      <c r="CU17" s="1"/>
+      <c r="CV17" s="1"/>
+      <c r="CW17" s="1"/>
+      <c r="CX17" s="1"/>
+      <c r="CY17" s="1"/>
+      <c r="CZ17" s="1"/>
+      <c r="DA17" s="1"/>
+      <c r="DB17" s="1"/>
+      <c r="DC17" s="1"/>
+      <c r="DD17" s="1"/>
+      <c r="DE17" s="1"/>
+      <c r="DF17" s="1"/>
+      <c r="DG17" s="1"/>
+      <c r="DH17" s="1"/>
+      <c r="DI17" s="1"/>
+      <c r="DJ17" s="1"/>
+      <c r="DK17" s="1"/>
+      <c r="DL17" s="1"/>
+      <c r="DM17" s="1"/>
+      <c r="DN17" s="1"/>
+      <c r="DO17" s="1"/>
+      <c r="DP17" s="1"/>
+      <c r="DQ17" s="1"/>
+      <c r="DR17" s="1"/>
+      <c r="DS17" s="1"/>
+      <c r="DT17" s="1"/>
+      <c r="DU17" s="1"/>
+      <c r="DV17" s="1"/>
+      <c r="DW17" s="1"/>
+      <c r="DX17" s="1"/>
+      <c r="DY17" s="1"/>
+      <c r="DZ17" s="1"/>
+      <c r="EA17" s="1"/>
+      <c r="EB17" s="1"/>
+      <c r="EC17" s="1"/>
+      <c r="ED17" s="1"/>
+      <c r="EE17" s="1"/>
+      <c r="EF17" s="1"/>
+      <c r="EG17" s="1"/>
+      <c r="EH17" s="1"/>
+      <c r="EI17" s="1"/>
+      <c r="EJ17" s="1"/>
+      <c r="EK17" s="1"/>
+      <c r="EL17" s="1"/>
+      <c r="EM17" s="1"/>
+      <c r="EN17" s="1"/>
+      <c r="EO17" s="1"/>
+      <c r="EP17" s="1"/>
+      <c r="EQ17" s="1"/>
+      <c r="ER17" s="1"/>
+      <c r="ES17" s="1"/>
+      <c r="ET17" s="1"/>
+      <c r="EU17" s="1"/>
+      <c r="EV17" s="1"/>
+      <c r="EW17" s="1"/>
+      <c r="EX17" s="1"/>
+      <c r="EY17" s="1"/>
+      <c r="EZ17" s="1"/>
+      <c r="FA17" s="1"/>
+      <c r="FB17" s="1"/>
+      <c r="FC17" s="1"/>
+      <c r="FD17" s="1"/>
+      <c r="FE17" s="1"/>
+      <c r="FF17" s="1"/>
+      <c r="FG17" s="1"/>
+      <c r="FH17" s="1"/>
+      <c r="FI17" s="1"/>
+      <c r="FJ17" s="1"/>
+      <c r="FK17" s="1"/>
+      <c r="FL17" s="1"/>
+      <c r="FM17" s="1"/>
+      <c r="FN17" s="1"/>
+      <c r="FO17" s="1"/>
+      <c r="FP17" s="1"/>
+      <c r="FQ17" s="1"/>
+      <c r="FR17" s="1"/>
+      <c r="FS17" s="1"/>
+      <c r="FT17" s="1"/>
+      <c r="FU17" s="1"/>
+      <c r="FV17" s="1"/>
+      <c r="FW17" s="1"/>
+      <c r="FX17" s="1"/>
+      <c r="FY17" s="1"/>
+      <c r="FZ17" s="1"/>
+      <c r="GA17" s="1"/>
+      <c r="GB17" s="1"/>
+      <c r="GC17" s="1"/>
+      <c r="GD17" s="1"/>
+      <c r="GE17" s="1"/>
+      <c r="GF17" s="1"/>
+      <c r="GG17" s="1"/>
+      <c r="GH17" s="1"/>
+      <c r="GI17" s="1"/>
+      <c r="GJ17" s="1"/>
+      <c r="GK17" s="2"/>
+      <c r="GL17" s="2"/>
+      <c r="GM17" s="2"/>
+      <c r="GN17" s="2"/>
+      <c r="GO17" s="2"/>
+      <c r="GP17" s="2"/>
+      <c r="GQ17" s="2"/>
+      <c r="GR17" s="2"/>
+      <c r="GS17" s="2"/>
+      <c r="GT17" s="2"/>
+      <c r="GU17" s="2"/>
+      <c r="GV17" s="2"/>
+      <c r="GW17" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="GX17" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="GY17" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="GZ17" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="HA17" s="2"/>
+      <c r="HB17" s="2"/>
+      <c r="HC17" s="2"/>
+      <c r="HD17" s="2"/>
+      <c r="HE17" s="2"/>
+      <c r="HF17" s="2"/>
+      <c r="HG17" s="2"/>
+      <c r="HH17" s="2"/>
+      <c r="HI17" s="2"/>
+      <c r="HJ17" s="2"/>
+      <c r="HK17" s="2"/>
+      <c r="HL17" s="2"/>
+      <c r="HM17" s="2"/>
+      <c r="HN17" s="2"/>
+      <c r="HO17" s="2"/>
+      <c r="HP17" s="2"/>
+      <c r="HQ17" s="2"/>
+      <c r="HR17" s="2"/>
+      <c r="HS17" s="2"/>
+      <c r="HT17" s="2"/>
+      <c r="HU17" s="2"/>
+      <c r="HV17" s="2"/>
+      <c r="HW17" s="2"/>
+      <c r="HX17" s="2"/>
+      <c r="HY17" s="2"/>
+      <c r="HZ17" s="2"/>
+      <c r="IA17" s="2"/>
+      <c r="IB17" s="2"/>
+      <c r="IC17" s="2"/>
+      <c r="ID17" s="2"/>
+      <c r="IE17" s="2"/>
+      <c r="IF17" s="2"/>
+      <c r="IG17" s="2"/>
+      <c r="IH17" s="2"/>
+      <c r="II17" s="2"/>
+      <c r="IJ17" s="2"/>
+      <c r="IK17" s="2"/>
+      <c r="IL17" s="2"/>
+      <c r="IM17" s="2"/>
+      <c r="IN17" s="2"/>
+      <c r="IO17" s="2"/>
+      <c r="IP17" s="2"/>
+      <c r="IQ17" s="2"/>
+      <c r="IR17" s="2"/>
+      <c r="IS17" s="2"/>
+      <c r="IT17" s="2"/>
+      <c r="IU17" s="2"/>
+      <c r="IV17" s="2"/>
+      <c r="IW17" s="2"/>
+      <c r="IX17" s="2"/>
+      <c r="IY17" s="2"/>
+      <c r="IZ17" s="2"/>
+      <c r="JA17" s="2"/>
+      <c r="JB17" s="2"/>
+      <c r="JC17" s="2"/>
+      <c r="JD17" s="2"/>
+      <c r="JE17" s="2"/>
+      <c r="JF17" s="2"/>
+      <c r="JG17" s="2"/>
+      <c r="JH17" s="2"/>
+      <c r="JI17" s="1">
+        <v>3</v>
+      </c>
+      <c r="JJ17" s="1">
+        <v>3</v>
+      </c>
+      <c r="JK17" s="1">
+        <v>25</v>
+      </c>
+      <c r="JL17" s="1">
+        <v>2</v>
+      </c>
+      <c r="JM17" s="1">
+        <v>229</v>
+      </c>
+      <c r="JN17" s="1">
+        <v>31</v>
+      </c>
+      <c r="JO17" s="1"/>
+      <c r="JP17" s="1"/>
+      <c r="JQ17" s="1"/>
+      <c r="JR17" s="1"/>
+      <c r="JS17" s="1"/>
+      <c r="JT17" s="1"/>
+      <c r="JU17" s="1"/>
+      <c r="JV17" s="1"/>
+      <c r="JW17" s="1"/>
+      <c r="JX17" s="1"/>
+      <c r="JY17" s="1"/>
+      <c r="JZ17" s="1"/>
+      <c r="KA17" s="1"/>
+      <c r="KB17" s="1"/>
+      <c r="KC17" s="1"/>
+      <c r="KD17" s="1"/>
+      <c r="KE17" s="1"/>
+      <c r="KF17" s="1"/>
+      <c r="KG17" s="1">
+        <v>293</v>
+      </c>
+      <c r="KH17" s="3"/>
+      <c r="KI17" s="3">
+        <v>46097.741909721997</v>
+      </c>
+      <c r="KJ17" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="KK17" s="1">
+        <v>1</v>
+      </c>
+      <c r="KL17" s="1">
+        <v>0</v>
+      </c>
+      <c r="KM17" s="1">
+        <v>9</v>
+      </c>
+      <c r="KN17" s="1">
+        <v>9</v>
+      </c>
+      <c r="KO17" s="1">
+        <v>0</v>
+      </c>
+      <c r="KP17" s="1">
+        <v>0</v>
+      </c>
+      <c r="KQ17" s="4">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:303" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>959</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F18" s="3">
+        <v>46097.774780093001</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="P18" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="1">
+        <v>56</v>
+      </c>
+      <c r="V18" s="1">
+        <v>101</v>
+      </c>
+      <c r="W18" s="1">
+        <v>81</v>
+      </c>
+      <c r="X18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1">
+        <v>74</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>70</v>
+      </c>
+      <c r="AI18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="1"/>
+      <c r="AN18" s="1"/>
+      <c r="AO18" s="1"/>
+      <c r="AP18" s="1"/>
+      <c r="AQ18" s="1"/>
+      <c r="AR18" s="1"/>
+      <c r="AS18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW18" s="1"/>
+      <c r="AX18" s="1"/>
+      <c r="AY18" s="1"/>
+      <c r="AZ18" s="1"/>
+      <c r="BA18" s="1"/>
+      <c r="BB18" s="1"/>
+      <c r="BC18" s="1"/>
+      <c r="BD18" s="1"/>
+      <c r="BE18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BF18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BH18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BI18" s="1"/>
+      <c r="BJ18" s="1"/>
+      <c r="BK18" s="1"/>
+      <c r="BL18" s="1"/>
+      <c r="BM18" s="1"/>
+      <c r="BN18" s="1"/>
+      <c r="BO18" s="1"/>
+      <c r="BP18" s="1"/>
+      <c r="BQ18" s="1">
+        <v>101</v>
+      </c>
+      <c r="BR18" s="1">
+        <v>26</v>
+      </c>
+      <c r="BS18" s="1">
+        <v>84</v>
+      </c>
+      <c r="BT18" s="1">
+        <v>101</v>
+      </c>
+      <c r="BU18" s="1"/>
+      <c r="BV18" s="1"/>
+      <c r="BW18" s="1"/>
+      <c r="BX18" s="1"/>
+      <c r="BY18" s="1"/>
+      <c r="BZ18" s="1"/>
+      <c r="CA18" s="1"/>
+      <c r="CB18" s="1"/>
+      <c r="CC18" s="1">
+        <v>18</v>
+      </c>
+      <c r="CD18" s="1">
+        <v>1</v>
+      </c>
+      <c r="CE18" s="1">
+        <v>101</v>
+      </c>
+      <c r="CF18" s="1">
+        <v>71</v>
+      </c>
+      <c r="CG18" s="1"/>
+      <c r="CH18" s="1"/>
+      <c r="CI18" s="1"/>
+      <c r="CJ18" s="1"/>
+      <c r="CK18" s="1"/>
+      <c r="CL18" s="1"/>
+      <c r="CM18" s="1"/>
+      <c r="CN18" s="1"/>
+      <c r="CO18" s="1"/>
+      <c r="CP18" s="1"/>
+      <c r="CQ18" s="1"/>
+      <c r="CR18" s="1"/>
+      <c r="CS18" s="1"/>
+      <c r="CT18" s="1"/>
+      <c r="CU18" s="1"/>
+      <c r="CV18" s="1"/>
+      <c r="CW18" s="1"/>
+      <c r="CX18" s="1"/>
+      <c r="CY18" s="1"/>
+      <c r="CZ18" s="1"/>
+      <c r="DA18" s="1"/>
+      <c r="DB18" s="1"/>
+      <c r="DC18" s="1"/>
+      <c r="DD18" s="1"/>
+      <c r="DE18" s="1"/>
+      <c r="DF18" s="1"/>
+      <c r="DG18" s="1"/>
+      <c r="DH18" s="1"/>
+      <c r="DI18" s="1"/>
+      <c r="DJ18" s="1"/>
+      <c r="DK18" s="1"/>
+      <c r="DL18" s="1"/>
+      <c r="DM18" s="1"/>
+      <c r="DN18" s="1"/>
+      <c r="DO18" s="1"/>
+      <c r="DP18" s="1"/>
+      <c r="DQ18" s="1"/>
+      <c r="DR18" s="1"/>
+      <c r="DS18" s="1"/>
+      <c r="DT18" s="1"/>
+      <c r="DU18" s="1"/>
+      <c r="DV18" s="1"/>
+      <c r="DW18" s="1"/>
+      <c r="DX18" s="1"/>
+      <c r="DY18" s="1"/>
+      <c r="DZ18" s="1"/>
+      <c r="EA18" s="1"/>
+      <c r="EB18" s="1"/>
+      <c r="EC18" s="1"/>
+      <c r="ED18" s="1"/>
+      <c r="EE18" s="1"/>
+      <c r="EF18" s="1"/>
+      <c r="EG18" s="1"/>
+      <c r="EH18" s="1"/>
+      <c r="EI18" s="1"/>
+      <c r="EJ18" s="1"/>
+      <c r="EK18" s="1"/>
+      <c r="EL18" s="1"/>
+      <c r="EM18" s="1"/>
+      <c r="EN18" s="1"/>
+      <c r="EO18" s="1"/>
+      <c r="EP18" s="1"/>
+      <c r="EQ18" s="1"/>
+      <c r="ER18" s="1"/>
+      <c r="ES18" s="1"/>
+      <c r="ET18" s="1"/>
+      <c r="EU18" s="1"/>
+      <c r="EV18" s="1"/>
+      <c r="EW18" s="1"/>
+      <c r="EX18" s="1"/>
+      <c r="EY18" s="1"/>
+      <c r="EZ18" s="1"/>
+      <c r="FA18" s="1"/>
+      <c r="FB18" s="1"/>
+      <c r="FC18" s="1"/>
+      <c r="FD18" s="1"/>
+      <c r="FE18" s="1"/>
+      <c r="FF18" s="1"/>
+      <c r="FG18" s="1"/>
+      <c r="FH18" s="1"/>
+      <c r="FI18" s="1"/>
+      <c r="FJ18" s="1"/>
+      <c r="FK18" s="1"/>
+      <c r="FL18" s="1"/>
+      <c r="FM18" s="1"/>
+      <c r="FN18" s="1"/>
+      <c r="FO18" s="1"/>
+      <c r="FP18" s="1"/>
+      <c r="FQ18" s="1"/>
+      <c r="FR18" s="1"/>
+      <c r="FS18" s="1"/>
+      <c r="FT18" s="1"/>
+      <c r="FU18" s="1"/>
+      <c r="FV18" s="1"/>
+      <c r="FW18" s="1"/>
+      <c r="FX18" s="1"/>
+      <c r="FY18" s="1"/>
+      <c r="FZ18" s="1"/>
+      <c r="GA18" s="1"/>
+      <c r="GB18" s="1"/>
+      <c r="GC18" s="1"/>
+      <c r="GD18" s="1"/>
+      <c r="GE18" s="1"/>
+      <c r="GF18" s="1"/>
+      <c r="GG18" s="1"/>
+      <c r="GH18" s="1"/>
+      <c r="GI18" s="1"/>
+      <c r="GJ18" s="1"/>
+      <c r="GK18" s="2"/>
+      <c r="GL18" s="2"/>
+      <c r="GM18" s="2"/>
+      <c r="GN18" s="2"/>
+      <c r="GO18" s="2"/>
+      <c r="GP18" s="2"/>
+      <c r="GQ18" s="2"/>
+      <c r="GR18" s="2"/>
+      <c r="GS18" s="2"/>
+      <c r="GT18" s="2"/>
+      <c r="GU18" s="2"/>
+      <c r="GV18" s="2"/>
+      <c r="GW18" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="GX18" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="GY18" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="GZ18" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="HA18" s="2"/>
+      <c r="HB18" s="2"/>
+      <c r="HC18" s="2"/>
+      <c r="HD18" s="2"/>
+      <c r="HE18" s="2"/>
+      <c r="HF18" s="2"/>
+      <c r="HG18" s="2"/>
+      <c r="HH18" s="2"/>
+      <c r="HI18" s="2"/>
+      <c r="HJ18" s="2"/>
+      <c r="HK18" s="2"/>
+      <c r="HL18" s="2"/>
+      <c r="HM18" s="2"/>
+      <c r="HN18" s="2"/>
+      <c r="HO18" s="2"/>
+      <c r="HP18" s="2"/>
+      <c r="HQ18" s="2"/>
+      <c r="HR18" s="2"/>
+      <c r="HS18" s="2"/>
+      <c r="HT18" s="2"/>
+      <c r="HU18" s="2"/>
+      <c r="HV18" s="2"/>
+      <c r="HW18" s="2"/>
+      <c r="HX18" s="2"/>
+      <c r="HY18" s="2"/>
+      <c r="HZ18" s="2"/>
+      <c r="IA18" s="2"/>
+      <c r="IB18" s="2"/>
+      <c r="IC18" s="2"/>
+      <c r="ID18" s="2"/>
+      <c r="IE18" s="2"/>
+      <c r="IF18" s="2"/>
+      <c r="IG18" s="2"/>
+      <c r="IH18" s="2"/>
+      <c r="II18" s="2"/>
+      <c r="IJ18" s="2"/>
+      <c r="IK18" s="2"/>
+      <c r="IL18" s="2"/>
+      <c r="IM18" s="2"/>
+      <c r="IN18" s="2"/>
+      <c r="IO18" s="2"/>
+      <c r="IP18" s="2"/>
+      <c r="IQ18" s="2"/>
+      <c r="IR18" s="2"/>
+      <c r="IS18" s="2"/>
+      <c r="IT18" s="2"/>
+      <c r="IU18" s="2"/>
+      <c r="IV18" s="2"/>
+      <c r="IW18" s="2"/>
+      <c r="IX18" s="2"/>
+      <c r="IY18" s="2"/>
+      <c r="IZ18" s="2"/>
+      <c r="JA18" s="2"/>
+      <c r="JB18" s="2"/>
+      <c r="JC18" s="2"/>
+      <c r="JD18" s="2"/>
+      <c r="JE18" s="2"/>
+      <c r="JF18" s="2"/>
+      <c r="JG18" s="2"/>
+      <c r="JH18" s="2"/>
+      <c r="JI18" s="1">
+        <v>10</v>
+      </c>
+      <c r="JJ18" s="1">
+        <v>9</v>
+      </c>
+      <c r="JK18" s="1">
+        <v>35</v>
+      </c>
+      <c r="JL18" s="1">
+        <v>10</v>
+      </c>
+      <c r="JM18" s="1">
+        <v>155</v>
+      </c>
+      <c r="JN18" s="1">
+        <v>32</v>
+      </c>
+      <c r="JO18" s="1"/>
+      <c r="JP18" s="1"/>
+      <c r="JQ18" s="1"/>
+      <c r="JR18" s="1"/>
+      <c r="JS18" s="1"/>
+      <c r="JT18" s="1"/>
+      <c r="JU18" s="1"/>
+      <c r="JV18" s="1"/>
+      <c r="JW18" s="1"/>
+      <c r="JX18" s="1"/>
+      <c r="JY18" s="1"/>
+      <c r="JZ18" s="1"/>
+      <c r="KA18" s="1"/>
+      <c r="KB18" s="1"/>
+      <c r="KC18" s="1"/>
+      <c r="KD18" s="1"/>
+      <c r="KE18" s="1"/>
+      <c r="KF18" s="1"/>
+      <c r="KG18" s="1">
+        <v>251</v>
+      </c>
+      <c r="KH18" s="3"/>
+      <c r="KI18" s="3">
+        <v>46097.777696759003</v>
+      </c>
+      <c r="KJ18" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="KK18" s="1">
+        <v>1</v>
+      </c>
+      <c r="KL18" s="1">
+        <v>0</v>
+      </c>
+      <c r="KM18" s="1">
+        <v>9</v>
+      </c>
+      <c r="KN18" s="1">
+        <v>9</v>
+      </c>
+      <c r="KO18" s="1">
+        <v>0</v>
+      </c>
+      <c r="KP18" s="1">
+        <v>0</v>
+      </c>
+      <c r="KQ18" s="4">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:303" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>960</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F19" s="3">
+        <v>46097.862488425999</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>1</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="1">
+        <v>18</v>
+      </c>
+      <c r="V19" s="1">
+        <v>36</v>
+      </c>
+      <c r="W19" s="1">
+        <v>101</v>
+      </c>
+      <c r="X19" s="1">
+        <v>64</v>
+      </c>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1">
+        <v>56</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>84</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>57</v>
+      </c>
+      <c r="AJ19" s="1">
+        <v>89</v>
+      </c>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1"/>
+      <c r="AS19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU19" s="1">
+        <v>9</v>
+      </c>
+      <c r="AV19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW19" s="1"/>
+      <c r="AX19" s="1"/>
+      <c r="AY19" s="1"/>
+      <c r="AZ19" s="1"/>
+      <c r="BA19" s="1"/>
+      <c r="BB19" s="1"/>
+      <c r="BC19" s="1"/>
+      <c r="BD19" s="1"/>
+      <c r="BE19" s="1">
+        <v>89</v>
+      </c>
+      <c r="BF19" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG19" s="1">
+        <v>1</v>
+      </c>
+      <c r="BH19" s="1">
+        <v>1</v>
+      </c>
+      <c r="BI19" s="1"/>
+      <c r="BJ19" s="1"/>
+      <c r="BK19" s="1"/>
+      <c r="BL19" s="1"/>
+      <c r="BM19" s="1"/>
+      <c r="BN19" s="1"/>
+      <c r="BO19" s="1"/>
+      <c r="BP19" s="1"/>
+      <c r="BQ19" s="1">
+        <v>68</v>
+      </c>
+      <c r="BR19" s="1">
+        <v>81</v>
+      </c>
+      <c r="BS19" s="1">
+        <v>26</v>
+      </c>
+      <c r="BT19" s="1">
+        <v>50</v>
+      </c>
+      <c r="BU19" s="1"/>
+      <c r="BV19" s="1"/>
+      <c r="BW19" s="1"/>
+      <c r="BX19" s="1"/>
+      <c r="BY19" s="1"/>
+      <c r="BZ19" s="1"/>
+      <c r="CA19" s="1"/>
+      <c r="CB19" s="1"/>
+      <c r="CC19" s="1">
+        <v>49</v>
+      </c>
+      <c r="CD19" s="1">
+        <v>91</v>
+      </c>
+      <c r="CE19" s="1">
+        <v>1</v>
+      </c>
+      <c r="CF19" s="1">
+        <v>58</v>
+      </c>
+      <c r="CG19" s="1"/>
+      <c r="CH19" s="1"/>
+      <c r="CI19" s="1"/>
+      <c r="CJ19" s="1"/>
+      <c r="CK19" s="1"/>
+      <c r="CL19" s="1"/>
+      <c r="CM19" s="1"/>
+      <c r="CN19" s="1"/>
+      <c r="CO19" s="1"/>
+      <c r="CP19" s="1"/>
+      <c r="CQ19" s="1"/>
+      <c r="CR19" s="1"/>
+      <c r="CS19" s="1"/>
+      <c r="CT19" s="1"/>
+      <c r="CU19" s="1"/>
+      <c r="CV19" s="1"/>
+      <c r="CW19" s="1"/>
+      <c r="CX19" s="1"/>
+      <c r="CY19" s="1"/>
+      <c r="CZ19" s="1"/>
+      <c r="DA19" s="1"/>
+      <c r="DB19" s="1"/>
+      <c r="DC19" s="1"/>
+      <c r="DD19" s="1"/>
+      <c r="DE19" s="1"/>
+      <c r="DF19" s="1"/>
+      <c r="DG19" s="1"/>
+      <c r="DH19" s="1"/>
+      <c r="DI19" s="1"/>
+      <c r="DJ19" s="1"/>
+      <c r="DK19" s="1"/>
+      <c r="DL19" s="1"/>
+      <c r="DM19" s="1"/>
+      <c r="DN19" s="1"/>
+      <c r="DO19" s="1"/>
+      <c r="DP19" s="1"/>
+      <c r="DQ19" s="1"/>
+      <c r="DR19" s="1"/>
+      <c r="DS19" s="1"/>
+      <c r="DT19" s="1"/>
+      <c r="DU19" s="1"/>
+      <c r="DV19" s="1"/>
+      <c r="DW19" s="1"/>
+      <c r="DX19" s="1"/>
+      <c r="DY19" s="1"/>
+      <c r="DZ19" s="1"/>
+      <c r="EA19" s="1"/>
+      <c r="EB19" s="1"/>
+      <c r="EC19" s="1"/>
+      <c r="ED19" s="1"/>
+      <c r="EE19" s="1"/>
+      <c r="EF19" s="1"/>
+      <c r="EG19" s="1"/>
+      <c r="EH19" s="1"/>
+      <c r="EI19" s="1"/>
+      <c r="EJ19" s="1"/>
+      <c r="EK19" s="1"/>
+      <c r="EL19" s="1"/>
+      <c r="EM19" s="1"/>
+      <c r="EN19" s="1"/>
+      <c r="EO19" s="1"/>
+      <c r="EP19" s="1"/>
+      <c r="EQ19" s="1"/>
+      <c r="ER19" s="1"/>
+      <c r="ES19" s="1"/>
+      <c r="ET19" s="1"/>
+      <c r="EU19" s="1"/>
+      <c r="EV19" s="1"/>
+      <c r="EW19" s="1"/>
+      <c r="EX19" s="1"/>
+      <c r="EY19" s="1"/>
+      <c r="EZ19" s="1"/>
+      <c r="FA19" s="1"/>
+      <c r="FB19" s="1"/>
+      <c r="FC19" s="1"/>
+      <c r="FD19" s="1"/>
+      <c r="FE19" s="1"/>
+      <c r="FF19" s="1"/>
+      <c r="FG19" s="1"/>
+      <c r="FH19" s="1"/>
+      <c r="FI19" s="1"/>
+      <c r="FJ19" s="1"/>
+      <c r="FK19" s="1"/>
+      <c r="FL19" s="1"/>
+      <c r="FM19" s="1"/>
+      <c r="FN19" s="1"/>
+      <c r="FO19" s="1"/>
+      <c r="FP19" s="1"/>
+      <c r="FQ19" s="1"/>
+      <c r="FR19" s="1"/>
+      <c r="FS19" s="1"/>
+      <c r="FT19" s="1"/>
+      <c r="FU19" s="1"/>
+      <c r="FV19" s="1"/>
+      <c r="FW19" s="1"/>
+      <c r="FX19" s="1"/>
+      <c r="FY19" s="1"/>
+      <c r="FZ19" s="1"/>
+      <c r="GA19" s="1"/>
+      <c r="GB19" s="1"/>
+      <c r="GC19" s="1"/>
+      <c r="GD19" s="1"/>
+      <c r="GE19" s="1"/>
+      <c r="GF19" s="1"/>
+      <c r="GG19" s="1"/>
+      <c r="GH19" s="1"/>
+      <c r="GI19" s="1"/>
+      <c r="GJ19" s="1"/>
+      <c r="GK19" s="2"/>
+      <c r="GL19" s="2"/>
+      <c r="GM19" s="2"/>
+      <c r="GN19" s="2"/>
+      <c r="GO19" s="2"/>
+      <c r="GP19" s="2"/>
+      <c r="GQ19" s="2"/>
+      <c r="GR19" s="2"/>
+      <c r="GS19" s="2"/>
+      <c r="GT19" s="2"/>
+      <c r="GU19" s="2"/>
+      <c r="GV19" s="2"/>
+      <c r="GW19" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="GX19" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="GY19" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="GZ19" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="HA19" s="2"/>
+      <c r="HB19" s="2"/>
+      <c r="HC19" s="2"/>
+      <c r="HD19" s="2"/>
+      <c r="HE19" s="2"/>
+      <c r="HF19" s="2"/>
+      <c r="HG19" s="2"/>
+      <c r="HH19" s="2"/>
+      <c r="HI19" s="2"/>
+      <c r="HJ19" s="2"/>
+      <c r="HK19" s="2"/>
+      <c r="HL19" s="2"/>
+      <c r="HM19" s="2"/>
+      <c r="HN19" s="2"/>
+      <c r="HO19" s="2"/>
+      <c r="HP19" s="2"/>
+      <c r="HQ19" s="2"/>
+      <c r="HR19" s="2"/>
+      <c r="HS19" s="2"/>
+      <c r="HT19" s="2"/>
+      <c r="HU19" s="2"/>
+      <c r="HV19" s="2"/>
+      <c r="HW19" s="2"/>
+      <c r="HX19" s="2"/>
+      <c r="HY19" s="2"/>
+      <c r="HZ19" s="2"/>
+      <c r="IA19" s="2"/>
+      <c r="IB19" s="2"/>
+      <c r="IC19" s="2"/>
+      <c r="ID19" s="2"/>
+      <c r="IE19" s="2"/>
+      <c r="IF19" s="2"/>
+      <c r="IG19" s="2"/>
+      <c r="IH19" s="2"/>
+      <c r="II19" s="2"/>
+      <c r="IJ19" s="2"/>
+      <c r="IK19" s="2"/>
+      <c r="IL19" s="2"/>
+      <c r="IM19" s="2"/>
+      <c r="IN19" s="2"/>
+      <c r="IO19" s="2"/>
+      <c r="IP19" s="2"/>
+      <c r="IQ19" s="2"/>
+      <c r="IR19" s="2"/>
+      <c r="IS19" s="2"/>
+      <c r="IT19" s="2"/>
+      <c r="IU19" s="2"/>
+      <c r="IV19" s="2"/>
+      <c r="IW19" s="2"/>
+      <c r="IX19" s="2"/>
+      <c r="IY19" s="2"/>
+      <c r="IZ19" s="2"/>
+      <c r="JA19" s="2"/>
+      <c r="JB19" s="2"/>
+      <c r="JC19" s="2"/>
+      <c r="JD19" s="2"/>
+      <c r="JE19" s="2"/>
+      <c r="JF19" s="2"/>
+      <c r="JG19" s="2"/>
+      <c r="JH19" s="2"/>
+      <c r="JI19" s="1">
+        <v>4</v>
+      </c>
+      <c r="JJ19" s="1">
+        <v>2</v>
+      </c>
+      <c r="JK19" s="1">
+        <v>23</v>
+      </c>
+      <c r="JL19" s="1">
+        <v>2</v>
+      </c>
+      <c r="JM19" s="1">
+        <v>144</v>
+      </c>
+      <c r="JN19" s="1">
+        <v>22</v>
+      </c>
+      <c r="JO19" s="1"/>
+      <c r="JP19" s="1"/>
+      <c r="JQ19" s="1"/>
+      <c r="JR19" s="1"/>
+      <c r="JS19" s="1"/>
+      <c r="JT19" s="1"/>
+      <c r="JU19" s="1"/>
+      <c r="JV19" s="1"/>
+      <c r="JW19" s="1"/>
+      <c r="JX19" s="1"/>
+      <c r="JY19" s="1"/>
+      <c r="JZ19" s="1"/>
+      <c r="KA19" s="1"/>
+      <c r="KB19" s="1"/>
+      <c r="KC19" s="1"/>
+      <c r="KD19" s="1"/>
+      <c r="KE19" s="1"/>
+      <c r="KF19" s="1"/>
+      <c r="KG19" s="1">
+        <v>197</v>
+      </c>
+      <c r="KH19" s="3"/>
+      <c r="KI19" s="3">
+        <v>46097.864768519001</v>
+      </c>
+      <c r="KJ19" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="KK19" s="1">
+        <v>1</v>
+      </c>
+      <c r="KL19" s="1">
+        <v>0</v>
+      </c>
+      <c r="KM19" s="1">
+        <v>9</v>
+      </c>
+      <c r="KN19" s="1">
+        <v>9</v>
+      </c>
+      <c r="KO19" s="1">
+        <v>0</v>
+      </c>
+      <c r="KP19" s="1">
+        <v>0</v>
+      </c>
+      <c r="KQ19" s="4">
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:303" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>961</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F20" s="3">
+        <v>46097.869212963</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="P20" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="1">
+        <v>2</v>
+      </c>
+      <c r="V20" s="1">
+        <v>51</v>
+      </c>
+      <c r="W20" s="1">
+        <v>45</v>
+      </c>
+      <c r="X20" s="1">
+        <v>69</v>
+      </c>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1">
+        <v>89</v>
+      </c>
+      <c r="AH20" s="1">
+        <v>56</v>
+      </c>
+      <c r="AI20" s="1">
+        <v>56</v>
+      </c>
+      <c r="AJ20" s="1">
+        <v>52</v>
+      </c>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1"/>
+      <c r="AS20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AU20" s="1">
+        <v>22</v>
+      </c>
+      <c r="AV20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW20" s="1"/>
+      <c r="AX20" s="1"/>
+      <c r="AY20" s="1"/>
+      <c r="AZ20" s="1"/>
+      <c r="BA20" s="1"/>
+      <c r="BB20" s="1"/>
+      <c r="BC20" s="1"/>
+      <c r="BD20" s="1"/>
+      <c r="BE20" s="1">
+        <v>15</v>
+      </c>
+      <c r="BF20" s="1">
+        <v>2</v>
+      </c>
+      <c r="BG20" s="1">
+        <v>81</v>
+      </c>
+      <c r="BH20" s="1">
+        <v>1</v>
+      </c>
+      <c r="BI20" s="1"/>
+      <c r="BJ20" s="1"/>
+      <c r="BK20" s="1"/>
+      <c r="BL20" s="1"/>
+      <c r="BM20" s="1"/>
+      <c r="BN20" s="1"/>
+      <c r="BO20" s="1"/>
+      <c r="BP20" s="1"/>
+      <c r="BQ20" s="1">
+        <v>38</v>
+      </c>
+      <c r="BR20" s="1">
+        <v>15</v>
+      </c>
+      <c r="BS20" s="1">
+        <v>17</v>
+      </c>
+      <c r="BT20" s="1">
+        <v>33</v>
+      </c>
+      <c r="BU20" s="1"/>
+      <c r="BV20" s="1"/>
+      <c r="BW20" s="1"/>
+      <c r="BX20" s="1"/>
+      <c r="BY20" s="1"/>
+      <c r="BZ20" s="1"/>
+      <c r="CA20" s="1"/>
+      <c r="CB20" s="1"/>
+      <c r="CC20" s="1">
+        <v>1</v>
+      </c>
+      <c r="CD20" s="1">
+        <v>19</v>
+      </c>
+      <c r="CE20" s="1">
+        <v>1</v>
+      </c>
+      <c r="CF20" s="1">
+        <v>1</v>
+      </c>
+      <c r="CG20" s="1"/>
+      <c r="CH20" s="1"/>
+      <c r="CI20" s="1"/>
+      <c r="CJ20" s="1"/>
+      <c r="CK20" s="1"/>
+      <c r="CL20" s="1"/>
+      <c r="CM20" s="1"/>
+      <c r="CN20" s="1"/>
+      <c r="CO20" s="1"/>
+      <c r="CP20" s="1"/>
+      <c r="CQ20" s="1"/>
+      <c r="CR20" s="1"/>
+      <c r="CS20" s="1"/>
+      <c r="CT20" s="1"/>
+      <c r="CU20" s="1"/>
+      <c r="CV20" s="1"/>
+      <c r="CW20" s="1"/>
+      <c r="CX20" s="1"/>
+      <c r="CY20" s="1"/>
+      <c r="CZ20" s="1"/>
+      <c r="DA20" s="1"/>
+      <c r="DB20" s="1"/>
+      <c r="DC20" s="1"/>
+      <c r="DD20" s="1"/>
+      <c r="DE20" s="1"/>
+      <c r="DF20" s="1"/>
+      <c r="DG20" s="1"/>
+      <c r="DH20" s="1"/>
+      <c r="DI20" s="1"/>
+      <c r="DJ20" s="1"/>
+      <c r="DK20" s="1"/>
+      <c r="DL20" s="1"/>
+      <c r="DM20" s="1"/>
+      <c r="DN20" s="1"/>
+      <c r="DO20" s="1"/>
+      <c r="DP20" s="1"/>
+      <c r="DQ20" s="1"/>
+      <c r="DR20" s="1"/>
+      <c r="DS20" s="1"/>
+      <c r="DT20" s="1"/>
+      <c r="DU20" s="1"/>
+      <c r="DV20" s="1"/>
+      <c r="DW20" s="1"/>
+      <c r="DX20" s="1"/>
+      <c r="DY20" s="1"/>
+      <c r="DZ20" s="1"/>
+      <c r="EA20" s="1"/>
+      <c r="EB20" s="1"/>
+      <c r="EC20" s="1"/>
+      <c r="ED20" s="1"/>
+      <c r="EE20" s="1"/>
+      <c r="EF20" s="1"/>
+      <c r="EG20" s="1"/>
+      <c r="EH20" s="1"/>
+      <c r="EI20" s="1"/>
+      <c r="EJ20" s="1"/>
+      <c r="EK20" s="1"/>
+      <c r="EL20" s="1"/>
+      <c r="EM20" s="1"/>
+      <c r="EN20" s="1"/>
+      <c r="EO20" s="1"/>
+      <c r="EP20" s="1"/>
+      <c r="EQ20" s="1"/>
+      <c r="ER20" s="1"/>
+      <c r="ES20" s="1"/>
+      <c r="ET20" s="1"/>
+      <c r="EU20" s="1"/>
+      <c r="EV20" s="1"/>
+      <c r="EW20" s="1"/>
+      <c r="EX20" s="1"/>
+      <c r="EY20" s="1"/>
+      <c r="EZ20" s="1"/>
+      <c r="FA20" s="1"/>
+      <c r="FB20" s="1"/>
+      <c r="FC20" s="1"/>
+      <c r="FD20" s="1"/>
+      <c r="FE20" s="1"/>
+      <c r="FF20" s="1"/>
+      <c r="FG20" s="1"/>
+      <c r="FH20" s="1"/>
+      <c r="FI20" s="1"/>
+      <c r="FJ20" s="1"/>
+      <c r="FK20" s="1"/>
+      <c r="FL20" s="1"/>
+      <c r="FM20" s="1"/>
+      <c r="FN20" s="1"/>
+      <c r="FO20" s="1"/>
+      <c r="FP20" s="1"/>
+      <c r="FQ20" s="1"/>
+      <c r="FR20" s="1"/>
+      <c r="FS20" s="1"/>
+      <c r="FT20" s="1"/>
+      <c r="FU20" s="1"/>
+      <c r="FV20" s="1"/>
+      <c r="FW20" s="1"/>
+      <c r="FX20" s="1"/>
+      <c r="FY20" s="1"/>
+      <c r="FZ20" s="1"/>
+      <c r="GA20" s="1"/>
+      <c r="GB20" s="1"/>
+      <c r="GC20" s="1"/>
+      <c r="GD20" s="1"/>
+      <c r="GE20" s="1"/>
+      <c r="GF20" s="1"/>
+      <c r="GG20" s="1"/>
+      <c r="GH20" s="1"/>
+      <c r="GI20" s="1"/>
+      <c r="GJ20" s="1"/>
+      <c r="GK20" s="2"/>
+      <c r="GL20" s="2"/>
+      <c r="GM20" s="2"/>
+      <c r="GN20" s="2"/>
+      <c r="GO20" s="2"/>
+      <c r="GP20" s="2"/>
+      <c r="GQ20" s="2"/>
+      <c r="GR20" s="2"/>
+      <c r="GS20" s="2"/>
+      <c r="GT20" s="2"/>
+      <c r="GU20" s="2"/>
+      <c r="GV20" s="2"/>
+      <c r="GW20" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="GX20" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="GY20" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="GZ20" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="HA20" s="2"/>
+      <c r="HB20" s="2"/>
+      <c r="HC20" s="2"/>
+      <c r="HD20" s="2"/>
+      <c r="HE20" s="2"/>
+      <c r="HF20" s="2"/>
+      <c r="HG20" s="2"/>
+      <c r="HH20" s="2"/>
+      <c r="HI20" s="2"/>
+      <c r="HJ20" s="2"/>
+      <c r="HK20" s="2"/>
+      <c r="HL20" s="2"/>
+      <c r="HM20" s="2"/>
+      <c r="HN20" s="2"/>
+      <c r="HO20" s="2"/>
+      <c r="HP20" s="2"/>
+      <c r="HQ20" s="2"/>
+      <c r="HR20" s="2"/>
+      <c r="HS20" s="2"/>
+      <c r="HT20" s="2"/>
+      <c r="HU20" s="2"/>
+      <c r="HV20" s="2"/>
+      <c r="HW20" s="2"/>
+      <c r="HX20" s="2"/>
+      <c r="HY20" s="2"/>
+      <c r="HZ20" s="2"/>
+      <c r="IA20" s="2"/>
+      <c r="IB20" s="2"/>
+      <c r="IC20" s="2"/>
+      <c r="ID20" s="2"/>
+      <c r="IE20" s="2"/>
+      <c r="IF20" s="2"/>
+      <c r="IG20" s="2"/>
+      <c r="IH20" s="2"/>
+      <c r="II20" s="2"/>
+      <c r="IJ20" s="2"/>
+      <c r="IK20" s="2"/>
+      <c r="IL20" s="2"/>
+      <c r="IM20" s="2"/>
+      <c r="IN20" s="2"/>
+      <c r="IO20" s="2"/>
+      <c r="IP20" s="2"/>
+      <c r="IQ20" s="2"/>
+      <c r="IR20" s="2"/>
+      <c r="IS20" s="2"/>
+      <c r="IT20" s="2"/>
+      <c r="IU20" s="2"/>
+      <c r="IV20" s="2"/>
+      <c r="IW20" s="2"/>
+      <c r="IX20" s="2"/>
+      <c r="IY20" s="2"/>
+      <c r="IZ20" s="2"/>
+      <c r="JA20" s="2"/>
+      <c r="JB20" s="2"/>
+      <c r="JC20" s="2"/>
+      <c r="JD20" s="2"/>
+      <c r="JE20" s="2"/>
+      <c r="JF20" s="2"/>
+      <c r="JG20" s="2"/>
+      <c r="JH20" s="2"/>
+      <c r="JI20" s="1">
+        <v>10</v>
+      </c>
+      <c r="JJ20" s="1">
+        <v>14</v>
+      </c>
+      <c r="JK20" s="1">
+        <v>72</v>
+      </c>
+      <c r="JL20" s="1">
+        <v>13</v>
+      </c>
+      <c r="JM20" s="1">
+        <v>310</v>
+      </c>
+      <c r="JN20" s="1">
+        <v>39</v>
+      </c>
+      <c r="JO20" s="1"/>
+      <c r="JP20" s="1"/>
+      <c r="JQ20" s="1"/>
+      <c r="JR20" s="1"/>
+      <c r="JS20" s="1"/>
+      <c r="JT20" s="1"/>
+      <c r="JU20" s="1"/>
+      <c r="JV20" s="1"/>
+      <c r="JW20" s="1"/>
+      <c r="JX20" s="1"/>
+      <c r="JY20" s="1"/>
+      <c r="JZ20" s="1"/>
+      <c r="KA20" s="1"/>
+      <c r="KB20" s="1"/>
+      <c r="KC20" s="1"/>
+      <c r="KD20" s="1"/>
+      <c r="KE20" s="1"/>
+      <c r="KF20" s="1"/>
+      <c r="KG20" s="1">
+        <v>458</v>
+      </c>
+      <c r="KH20" s="3"/>
+      <c r="KI20" s="3">
+        <v>46097.874513889001</v>
+      </c>
+      <c r="KJ20" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="KK20" s="1">
+        <v>1</v>
+      </c>
+      <c r="KL20" s="1">
+        <v>0</v>
+      </c>
+      <c r="KM20" s="1">
+        <v>9</v>
+      </c>
+      <c r="KN20" s="1">
+        <v>9</v>
+      </c>
+      <c r="KO20" s="1">
+        <v>0</v>
+      </c>
+      <c r="KP20" s="1">
+        <v>0</v>
+      </c>
+      <c r="KQ20" s="4">
+        <v>0.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" scale="0" orientation="portrait" usePrinterDefaults="0" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/DAT/raw/data_BodyPerception_new.xlsx
+++ b/DAT/raw/data_BodyPerception_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/delphinehund/Desktop/Stage/Pilot_Study-SocBodPer/V2/code/DAT/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8AB31C-57D8-5E4F-A738-579923038E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AB290B-19CF-1949-823E-F126F4C0DC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11620" yWindow="2600" windowWidth="16380" windowHeight="16520" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="190">
   <si>
     <t>CASE</t>
   </si>
@@ -40,9 +40,6 @@
     <t>STARTED</t>
   </si>
   <si>
-    <t>CO01_01</t>
-  </si>
-  <si>
     <t>CO01_02</t>
   </si>
   <si>
@@ -223,9 +220,6 @@
     <t>Time the interview has started (Europe/Berlin)</t>
   </si>
   <si>
-    <t>Consentement: Je soussigné.e. ...</t>
-  </si>
-  <si>
     <t>Consentement: né.e. le ...</t>
   </si>
   <si>
@@ -367,24 +361,15 @@
     <t>Pre-Manip03</t>
   </si>
   <si>
-    <t>Matys Précloux</t>
-  </si>
-  <si>
     <t>13/03/2026</t>
   </si>
   <si>
-    <t>Léa pons</t>
-  </si>
-  <si>
     <t>05052001</t>
   </si>
   <si>
     <t>13/03/26</t>
   </si>
   <si>
-    <t>Aurélia Silva</t>
-  </si>
-  <si>
     <t>12/04/1999</t>
   </si>
   <si>
@@ -394,9 +379,6 @@
     <t>26</t>
   </si>
   <si>
-    <t>Aurélia pons</t>
-  </si>
-  <si>
     <t>06/04/2004</t>
   </si>
   <si>
@@ -406,9 +388,6 @@
     <t>21</t>
   </si>
   <si>
-    <t>Laborde Mélanie</t>
-  </si>
-  <si>
     <t>19/05/1977</t>
   </si>
   <si>
@@ -418,9 +397,6 @@
     <t>48</t>
   </si>
   <si>
-    <t>DUMONTEIL Evelyne</t>
-  </si>
-  <si>
     <t>29/07/1956</t>
   </si>
   <si>
@@ -430,9 +406,6 @@
     <t>69</t>
   </si>
   <si>
-    <t>StephanieCHOUCHANE</t>
-  </si>
-  <si>
     <t>07/01/1975</t>
   </si>
   <si>
@@ -442,9 +415,6 @@
     <t>51</t>
   </si>
   <si>
-    <t>Carole pons</t>
-  </si>
-  <si>
     <t>25/08/1970</t>
   </si>
   <si>
@@ -457,9 +427,6 @@
     <t>55</t>
   </si>
   <si>
-    <t>Roselyne tersol</t>
-  </si>
-  <si>
     <t>23/06/1957</t>
   </si>
   <si>
@@ -469,9 +436,6 @@
     <t>68</t>
   </si>
   <si>
-    <t>Hund Jf</t>
-  </si>
-  <si>
     <t>29 mars 1967</t>
   </si>
   <si>
@@ -484,9 +448,6 @@
     <t>58</t>
   </si>
   <si>
-    <t>Manon Nicolle</t>
-  </si>
-  <si>
     <t>15/01/2003</t>
   </si>
   <si>
@@ -499,9 +460,6 @@
     <t>23</t>
   </si>
   <si>
-    <t>Marjorie Carratie</t>
-  </si>
-  <si>
     <t>08/12/1976</t>
   </si>
   <si>
@@ -514,9 +472,6 @@
     <t>49</t>
   </si>
   <si>
-    <t>Costes carine</t>
-  </si>
-  <si>
     <t>23 02 1976</t>
   </si>
   <si>
@@ -529,9 +484,6 @@
     <t>50</t>
   </si>
   <si>
-    <t>Gaetan Vergnon</t>
-  </si>
-  <si>
     <t>05/03/2001</t>
   </si>
   <si>
@@ -544,27 +496,18 @@
     <t>25</t>
   </si>
   <si>
-    <t>Hund Sébastien</t>
-  </si>
-  <si>
     <t>11-09/2000</t>
   </si>
   <si>
     <t>HUSE</t>
   </si>
   <si>
-    <t>Dubief</t>
-  </si>
-  <si>
     <t>22/11/2001</t>
   </si>
   <si>
     <t>DUBL</t>
   </si>
   <si>
-    <t>Jocelyn Precloux</t>
-  </si>
-  <si>
     <t>06/03/1970</t>
   </si>
   <si>
@@ -574,9 +517,6 @@
     <t>56</t>
   </si>
   <si>
-    <t>cathy rouleau</t>
-  </si>
-  <si>
     <t>14121962</t>
   </si>
   <si>
@@ -589,9 +529,6 @@
     <t>63</t>
   </si>
   <si>
-    <t>Thomas Colin</t>
-  </si>
-  <si>
     <t>14/09/2000</t>
   </si>
   <si>
@@ -601,27 +538,18 @@
     <t>THCO</t>
   </si>
   <si>
-    <t>Roger Tristan</t>
-  </si>
-  <si>
     <t>18/01/2002</t>
   </si>
   <si>
     <t>RoTr</t>
   </si>
   <si>
-    <t>Jules Goumard</t>
-  </si>
-  <si>
     <t>31/12/2001</t>
   </si>
   <si>
     <t>GOJU</t>
   </si>
   <si>
-    <t>nicolas brianc</t>
-  </si>
-  <si>
     <t>21 janvier 1981</t>
   </si>
   <si>
@@ -634,9 +562,6 @@
     <t>45</t>
   </si>
   <si>
-    <t>denis jade</t>
-  </si>
-  <si>
     <t>22/08/2004</t>
   </si>
   <si>
@@ -646,9 +571,6 @@
     <t>DEJA</t>
   </si>
   <si>
-    <t>Guitteaud Mathis</t>
-  </si>
-  <si>
     <t>14/09/2004</t>
   </si>
   <si>
@@ -656,9 +578,6 @@
   </si>
   <si>
     <t>GUMA</t>
-  </si>
-  <si>
-    <t>Dejan Loriane</t>
   </si>
   <si>
     <t>8 février 2006</t>
@@ -1048,28 +967,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ27"/>
+  <dimension ref="A1:BI27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="9" width="32" customWidth="1"/>
-    <col min="10" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
-    <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="32" customWidth="1"/>
-    <col min="16" max="41" width="8" customWidth="1"/>
-    <col min="42" max="45" width="32" customWidth="1"/>
-    <col min="46" max="52" width="5" customWidth="1"/>
-    <col min="53" max="53" width="20" customWidth="1"/>
-    <col min="54" max="54" width="16" customWidth="1"/>
-    <col min="55" max="61" width="8" customWidth="1"/>
-    <col min="62" max="782" width="11.5"/>
+    <col min="7" max="8" width="32" customWidth="1"/>
+    <col min="9" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="32" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
+    <col min="15" max="40" width="8" customWidth="1"/>
+    <col min="41" max="44" width="32" customWidth="1"/>
+    <col min="45" max="51" width="5" customWidth="1"/>
+    <col min="52" max="52" width="20" customWidth="1"/>
+    <col min="53" max="53" width="16" customWidth="1"/>
+    <col min="54" max="60" width="8" customWidth="1"/>
+    <col min="61" max="781" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1250,218 +1169,212 @@
       <c r="BH1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+    </row>
+    <row r="2" spans="1:60" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH2" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA2" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI2" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>817</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F3" s="3">
         <v>46094.692685185</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
@@ -1469,178 +1382,175 @@
       <c r="K3" s="1">
         <v>1</v>
       </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>106</v>
+      <c r="L3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2</v>
       </c>
       <c r="P3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>27</v>
+      </c>
+      <c r="R3" s="1">
+        <v>54</v>
+      </c>
+      <c r="S3" s="1">
+        <v>55</v>
+      </c>
+      <c r="T3" s="1">
+        <v>101</v>
+      </c>
+      <c r="U3" s="1">
+        <v>46</v>
+      </c>
+      <c r="V3" s="1">
+        <v>49</v>
+      </c>
+      <c r="W3" s="1">
+        <v>50</v>
+      </c>
+      <c r="X3" s="1">
+        <v>43</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="1">
         <v>2</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>1</v>
-      </c>
-      <c r="R3" s="1">
-        <v>27</v>
-      </c>
-      <c r="S3" s="1">
-        <v>54</v>
-      </c>
-      <c r="T3" s="1">
-        <v>55</v>
-      </c>
-      <c r="U3" s="1">
-        <v>101</v>
-      </c>
-      <c r="V3" s="1">
-        <v>46</v>
-      </c>
-      <c r="W3" s="1">
-        <v>49</v>
-      </c>
-      <c r="X3" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>43</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="1">
-        <v>23</v>
       </c>
       <c r="AD3" s="1">
         <v>2</v>
       </c>
       <c r="AE3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>101</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>95</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>80</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>101</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>58</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AS3" s="1">
         <v>2</v>
-      </c>
-      <c r="AF3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="1">
-        <v>101</v>
-      </c>
-      <c r="AI3" s="1">
-        <v>95</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>80</v>
-      </c>
-      <c r="AK3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AL3" s="1">
-        <v>101</v>
-      </c>
-      <c r="AM3" s="1">
-        <v>58</v>
-      </c>
-      <c r="AN3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO3" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="AT3" s="1">
         <v>2</v>
       </c>
       <c r="AU3" s="1">
+        <v>16</v>
+      </c>
+      <c r="AV3" s="1">
         <v>2</v>
       </c>
-      <c r="AV3" s="1">
-        <v>16</v>
-      </c>
       <c r="AW3" s="1">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="AX3" s="1">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="AY3" s="1">
-        <v>25</v>
-      </c>
-      <c r="AZ3" s="1">
         <v>232</v>
       </c>
-      <c r="BA3" s="3">
+      <c r="AZ3" s="3">
         <v>46094.695370369998</v>
       </c>
-      <c r="BB3" s="2" t="s">
-        <v>105</v>
+      <c r="BA3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>1</v>
       </c>
       <c r="BC3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE3" s="1">
         <v>9</v>
       </c>
       <c r="BF3" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG3" s="1">
         <v>0</v>
       </c>
-      <c r="BH3" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="4"/>
+      <c r="BH3" s="4"/>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>818</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3">
         <v>46094.696296296002</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
@@ -1648,178 +1558,175 @@
       <c r="K4" s="1">
         <v>1</v>
       </c>
-      <c r="L4" s="1">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>106</v>
+      <c r="L4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
       </c>
       <c r="P4" s="1">
         <v>1</v>
       </c>
       <c r="Q4" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R4" s="1">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="S4" s="1">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="T4" s="1">
+        <v>101</v>
+      </c>
+      <c r="U4" s="1">
+        <v>41</v>
+      </c>
+      <c r="V4" s="1">
+        <v>57</v>
+      </c>
+      <c r="W4" s="1">
+        <v>77</v>
+      </c>
+      <c r="X4" s="1">
         <v>38</v>
       </c>
-      <c r="U4" s="1">
-        <v>101</v>
-      </c>
-      <c r="V4" s="1">
-        <v>41</v>
-      </c>
-      <c r="W4" s="1">
-        <v>57</v>
-      </c>
-      <c r="X4" s="1">
-        <v>77</v>
-      </c>
       <c r="Y4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>32</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>13</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>87</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>91</v>
+      </c>
+      <c r="AJ4" s="1">
         <v>38</v>
       </c>
-      <c r="Z4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>32</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG4" s="1">
+      <c r="AK4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>65</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>64</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>39</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>28</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>154</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>26</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>255</v>
+      </c>
+      <c r="AZ4" s="3">
+        <v>46094.699247684999</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB4" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="1">
         <v>9</v>
-      </c>
-      <c r="AH4" s="1">
-        <v>13</v>
-      </c>
-      <c r="AI4" s="1">
-        <v>87</v>
-      </c>
-      <c r="AJ4" s="1">
-        <v>91</v>
-      </c>
-      <c r="AK4" s="1">
-        <v>38</v>
-      </c>
-      <c r="AL4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM4" s="1">
-        <v>65</v>
-      </c>
-      <c r="AN4" s="1">
-        <v>64</v>
-      </c>
-      <c r="AO4" s="1">
-        <v>3</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AT4" s="1">
-        <v>5</v>
-      </c>
-      <c r="AU4" s="1">
-        <v>3</v>
-      </c>
-      <c r="AV4" s="1">
-        <v>39</v>
-      </c>
-      <c r="AW4" s="1">
-        <v>28</v>
-      </c>
-      <c r="AX4" s="1">
-        <v>154</v>
-      </c>
-      <c r="AY4" s="1">
-        <v>26</v>
-      </c>
-      <c r="AZ4" s="1">
-        <v>255</v>
-      </c>
-      <c r="BA4" s="3">
-        <v>46094.699247684999</v>
-      </c>
-      <c r="BB4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BC4" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD4" s="1">
-        <v>0</v>
       </c>
       <c r="BE4" s="1">
         <v>9</v>
       </c>
       <c r="BF4" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG4" s="1">
         <v>0</v>
       </c>
-      <c r="BH4" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="4"/>
+      <c r="BH4" s="4"/>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>822</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F5" s="3">
         <v>46094.705127314999</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -1827,23 +1734,23 @@
       <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>123</v>
+      <c r="L5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
       </c>
       <c r="P5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" s="1">
         <v>1</v>
@@ -1852,28 +1759,28 @@
         <v>1</v>
       </c>
       <c r="T5" s="1">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="U5" s="1">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="V5" s="1">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="W5" s="1">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="X5" s="1">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="Y5" s="1">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="Z5" s="1">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="AA5" s="1">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="1">
         <v>1</v>
@@ -1897,110 +1804,107 @@
         <v>1</v>
       </c>
       <c r="AI5" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AJ5" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AK5" s="1">
         <v>1</v>
       </c>
       <c r="AL5" s="1">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AM5" s="1">
         <v>101</v>
       </c>
       <c r="AN5" s="1">
-        <v>101</v>
-      </c>
-      <c r="AO5" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="AP5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AQ5" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="AR5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS5" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>19</v>
       </c>
       <c r="AT5" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AU5" s="1">
+        <v>29</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>6</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>190</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>37</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>290</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>46094.708483795999</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="1">
         <v>9</v>
-      </c>
-      <c r="AV5" s="1">
-        <v>29</v>
-      </c>
-      <c r="AW5" s="1">
-        <v>6</v>
-      </c>
-      <c r="AX5" s="1">
-        <v>190</v>
-      </c>
-      <c r="AY5" s="1">
-        <v>37</v>
-      </c>
-      <c r="AZ5" s="1">
-        <v>290</v>
-      </c>
-      <c r="BA5" s="3">
-        <v>46094.708483795999</v>
-      </c>
-      <c r="BB5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BC5" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="1">
-        <v>0</v>
       </c>
       <c r="BE5" s="1">
         <v>9</v>
       </c>
       <c r="BF5" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG5" s="1">
         <v>0</v>
       </c>
-      <c r="BH5" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="4">
+      <c r="BH5" s="4">
         <v>0.98</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>829</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F6" s="3">
         <v>46094.713125000002</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -2008,180 +1912,177 @@
       <c r="K6" s="1">
         <v>1</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>127</v>
+      <c r="L6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
       </c>
       <c r="P6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="1">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="R6" s="1">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="S6" s="1">
         <v>1</v>
       </c>
       <c r="T6" s="1">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="U6" s="1">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="V6" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="W6" s="1">
+        <v>28</v>
+      </c>
+      <c r="X6" s="1">
+        <v>91</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>55</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>61</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>29</v>
+      </c>
+      <c r="AH6" s="1">
         <v>48</v>
       </c>
-      <c r="X6" s="1">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>91</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>55</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>61</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>29</v>
-      </c>
       <c r="AI6" s="1">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="AJ6" s="1">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="AK6" s="1">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="AL6" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM6" s="1">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="AN6" s="1">
-        <v>19</v>
-      </c>
-      <c r="AO6" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="AP6" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AQ6" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AR6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS6" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>2</v>
       </c>
       <c r="AT6" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AU6" s="1">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="AV6" s="1">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="AW6" s="1">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="AX6" s="1">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="AY6" s="1">
-        <v>53</v>
-      </c>
-      <c r="AZ6" s="1">
         <v>328</v>
       </c>
-      <c r="BA6" s="3">
+      <c r="AZ6" s="3">
         <v>46094.716921296</v>
       </c>
-      <c r="BB6" s="2" t="s">
-        <v>105</v>
+      <c r="BA6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>1</v>
       </c>
       <c r="BC6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD6" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE6" s="1">
         <v>9</v>
       </c>
       <c r="BF6" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG6" s="1">
         <v>0</v>
       </c>
-      <c r="BH6" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="4">
+      <c r="BH6" s="4">
         <v>1.29</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>836</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" s="3">
         <v>46094.714803240997</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
@@ -2189,180 +2090,177 @@
       <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>131</v>
+      <c r="L7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
       </c>
       <c r="P7" s="1">
         <v>1</v>
       </c>
       <c r="Q7" s="1">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="R7" s="1">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="S7" s="1">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="T7" s="1">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="U7" s="1">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="V7" s="1">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="W7" s="1">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="X7" s="1">
         <v>81</v>
       </c>
       <c r="Y7" s="1">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="1">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="AA7" s="1">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AC7" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="AE7" s="1">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="AF7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG7" s="1">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="AH7" s="1">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="AI7" s="1">
+        <v>70</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>76</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>101</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>61</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>30</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>21</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>12</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>28</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>57</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>15</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>276</v>
+      </c>
+      <c r="AX7" s="1">
         <v>34</v>
       </c>
-      <c r="AJ7" s="1">
-        <v>70</v>
-      </c>
-      <c r="AK7" s="1">
-        <v>76</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>101</v>
-      </c>
-      <c r="AM7" s="1">
-        <v>61</v>
-      </c>
-      <c r="AN7" s="1">
-        <v>30</v>
-      </c>
-      <c r="AO7" s="1">
-        <v>21</v>
-      </c>
-      <c r="AP7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AT7" s="1">
-        <v>12</v>
-      </c>
-      <c r="AU7" s="1">
-        <v>28</v>
-      </c>
-      <c r="AV7" s="1">
-        <v>57</v>
-      </c>
-      <c r="AW7" s="1">
-        <v>15</v>
-      </c>
-      <c r="AX7" s="1">
-        <v>276</v>
-      </c>
       <c r="AY7" s="1">
-        <v>34</v>
-      </c>
-      <c r="AZ7" s="1">
         <v>422</v>
       </c>
-      <c r="BA7" s="3">
+      <c r="AZ7" s="3">
         <v>46094.719687500001</v>
       </c>
-      <c r="BB7" s="2" t="s">
-        <v>105</v>
+      <c r="BA7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>1</v>
       </c>
       <c r="BC7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD7" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE7" s="1">
         <v>9</v>
       </c>
       <c r="BF7" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG7" s="1">
         <v>0</v>
       </c>
-      <c r="BH7" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="4">
+      <c r="BH7" s="4">
         <v>0.64</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>852</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F8" s="3">
         <v>46094.721388888996</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -2370,17 +2268,17 @@
       <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="1">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>135</v>
+      <c r="L8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <v>1</v>
@@ -2389,161 +2287,158 @@
         <v>1</v>
       </c>
       <c r="R8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S8" s="1">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="T8" s="1">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="U8" s="1">
+        <v>19</v>
+      </c>
+      <c r="V8" s="1">
+        <v>48</v>
+      </c>
+      <c r="W8" s="1">
+        <v>54</v>
+      </c>
+      <c r="X8" s="1">
+        <v>81</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>7</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>9</v>
+      </c>
+      <c r="AE8" s="1">
         <v>23</v>
       </c>
-      <c r="V8" s="1">
-        <v>19</v>
-      </c>
-      <c r="W8" s="1">
-        <v>48</v>
-      </c>
-      <c r="X8" s="1">
-        <v>54</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>81</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>7</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="1">
-        <v>9</v>
-      </c>
       <c r="AF8" s="1">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AG8" s="1">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AH8" s="1">
         <v>101</v>
       </c>
       <c r="AI8" s="1">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AJ8" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AK8" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AL8" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AM8" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN8" s="1">
+        <v>11</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>10</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>23</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>46</v>
+      </c>
+      <c r="AV8" s="1">
         <v>7</v>
       </c>
-      <c r="AO8" s="1">
-        <v>11</v>
-      </c>
-      <c r="AP8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT8" s="1">
-        <v>10</v>
-      </c>
-      <c r="AU8" s="1">
-        <v>23</v>
-      </c>
-      <c r="AV8" s="1">
-        <v>46</v>
-      </c>
       <c r="AW8" s="1">
-        <v>7</v>
+        <v>213</v>
       </c>
       <c r="AX8" s="1">
-        <v>213</v>
+        <v>30</v>
       </c>
       <c r="AY8" s="1">
-        <v>30</v>
-      </c>
-      <c r="AZ8" s="1">
         <v>329</v>
       </c>
-      <c r="BA8" s="3">
+      <c r="AZ8" s="3">
         <v>46094.725196758998</v>
       </c>
-      <c r="BB8" s="2" t="s">
-        <v>105</v>
+      <c r="BA8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB8" s="1">
+        <v>1</v>
       </c>
       <c r="BC8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE8" s="1">
         <v>9</v>
       </c>
       <c r="BF8" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG8" s="1">
         <v>0</v>
       </c>
-      <c r="BH8" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="4">
+      <c r="BH8" s="4">
         <v>0.84</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>864</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F9" s="3">
         <v>46094.744722222</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -2551,180 +2446,177 @@
       <c r="K9" s="1">
         <v>1</v>
       </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="N9" s="1">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>139</v>
+      <c r="L9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
       </c>
       <c r="P9" s="1">
         <v>1</v>
       </c>
       <c r="Q9" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R9" s="1">
+        <v>19</v>
+      </c>
+      <c r="S9" s="1">
         <v>24</v>
       </c>
-      <c r="S9" s="1">
-        <v>19</v>
-      </c>
       <c r="T9" s="1">
+        <v>77</v>
+      </c>
+      <c r="U9" s="1">
+        <v>82</v>
+      </c>
+      <c r="V9" s="1">
         <v>24</v>
       </c>
-      <c r="U9" s="1">
-        <v>77</v>
-      </c>
-      <c r="V9" s="1">
-        <v>82</v>
-      </c>
       <c r="W9" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="X9" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Y9" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>16</v>
+      </c>
+      <c r="AC9" s="1">
         <v>2</v>
       </c>
-      <c r="AB9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>16</v>
-      </c>
       <c r="AD9" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="1">
         <v>2</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>3</v>
       </c>
       <c r="AF9" s="1">
         <v>2</v>
       </c>
       <c r="AG9" s="1">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="AH9" s="1">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="AI9" s="1">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="AJ9" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK9" s="1">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AL9" s="1">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AM9" s="1">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="AN9" s="1">
-        <v>21</v>
-      </c>
-      <c r="AO9" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="AP9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AQ9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS9" s="2" t="s">
-        <v>113</v>
+      <c r="AS9" s="1">
+        <v>11</v>
       </c>
       <c r="AT9" s="1">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="AU9" s="1">
         <v>38</v>
       </c>
       <c r="AV9" s="1">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="AW9" s="1">
-        <v>7</v>
+        <v>151</v>
       </c>
       <c r="AX9" s="1">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="AY9" s="1">
-        <v>41</v>
-      </c>
-      <c r="AZ9" s="1">
         <v>286</v>
       </c>
-      <c r="BA9" s="3">
+      <c r="AZ9" s="3">
         <v>46094.748032406998</v>
       </c>
-      <c r="BB9" s="2" t="s">
-        <v>105</v>
+      <c r="BA9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>1</v>
       </c>
       <c r="BC9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE9" s="1">
         <v>9</v>
       </c>
       <c r="BF9" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG9" s="1">
         <v>0</v>
       </c>
-      <c r="BH9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="4">
+      <c r="BH9" s="4">
         <v>0.85</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>877</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F10" s="3">
         <v>46094.818506944001</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -2732,180 +2624,177 @@
       <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="N10" s="1">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>144</v>
+      <c r="L10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
       </c>
       <c r="P10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" s="1">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="S10" s="1">
+        <v>1</v>
+      </c>
+      <c r="T10" s="1">
         <v>101</v>
-      </c>
-      <c r="T10" s="1">
-        <v>1</v>
       </c>
       <c r="U10" s="1">
         <v>101</v>
       </c>
       <c r="V10" s="1">
+        <v>5</v>
+      </c>
+      <c r="W10" s="1">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>83</v>
+      </c>
+      <c r="AH10" s="1">
         <v>101</v>
-      </c>
-      <c r="W10" s="1">
-        <v>5</v>
-      </c>
-      <c r="X10" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="1">
-        <v>83</v>
       </c>
       <c r="AI10" s="1">
         <v>101</v>
       </c>
       <c r="AJ10" s="1">
+        <v>81</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="1">
         <v>101</v>
       </c>
-      <c r="AK10" s="1">
-        <v>81</v>
-      </c>
-      <c r="AL10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM10" s="1">
-        <v>1</v>
-      </c>
       <c r="AN10" s="1">
-        <v>101</v>
-      </c>
-      <c r="AO10" s="1">
         <v>3</v>
       </c>
+      <c r="AO10" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="AP10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AQ10" s="2" t="s">
+      <c r="AR10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AR10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS10" s="2" t="s">
-        <v>113</v>
+      <c r="AS10" s="1">
+        <v>5</v>
       </c>
       <c r="AT10" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AU10" s="1">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AV10" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AW10" s="1">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="AX10" s="1">
-        <v>198</v>
+        <v>37</v>
       </c>
       <c r="AY10" s="1">
-        <v>37</v>
-      </c>
-      <c r="AZ10" s="1">
         <v>291</v>
       </c>
-      <c r="BA10" s="3">
+      <c r="AZ10" s="3">
         <v>46094.821875000001</v>
       </c>
-      <c r="BB10" s="2" t="s">
-        <v>105</v>
+      <c r="BA10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB10" s="1">
+        <v>1</v>
       </c>
       <c r="BC10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD10" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE10" s="1">
         <v>9</v>
       </c>
       <c r="BF10" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG10" s="1">
         <v>0</v>
       </c>
-      <c r="BH10" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="4">
+      <c r="BH10" s="4">
         <v>1.03</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>881</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F11" s="3">
         <v>46094.940335648003</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -2913,180 +2802,177 @@
       <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>148</v>
+      <c r="L11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1</v>
       </c>
       <c r="P11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="1">
+        <v>6</v>
+      </c>
+      <c r="R11" s="1">
         <v>2</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
+        <v>59</v>
+      </c>
+      <c r="T11" s="1">
+        <v>45</v>
+      </c>
+      <c r="U11" s="1">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>22</v>
+      </c>
+      <c r="W11" s="1">
+        <v>80</v>
+      </c>
+      <c r="X11" s="1">
+        <v>72</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="1">
         <v>6</v>
       </c>
-      <c r="S11" s="1">
+      <c r="AD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="1">
         <v>2</v>
       </c>
-      <c r="T11" s="1">
-        <v>59</v>
-      </c>
-      <c r="U11" s="1">
-        <v>45</v>
-      </c>
-      <c r="V11" s="1">
-        <v>1</v>
-      </c>
-      <c r="W11" s="1">
-        <v>22</v>
-      </c>
-      <c r="X11" s="1">
-        <v>80</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>72</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>6</v>
-      </c>
-      <c r="AE11" s="1">
-        <v>1</v>
-      </c>
       <c r="AF11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG11" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AH11" s="1">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AI11" s="1">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="AJ11" s="1">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="AK11" s="1">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AL11" s="1">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AM11" s="1">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO11" s="1">
         <v>13</v>
       </c>
+      <c r="AO11" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="AP11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AQ11" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="AR11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS11" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>8</v>
       </c>
       <c r="AT11" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AU11" s="1">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="AV11" s="1">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="AW11" s="1">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="AX11" s="1">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="AY11" s="1">
-        <v>53</v>
-      </c>
-      <c r="AZ11" s="1">
         <v>256</v>
       </c>
-      <c r="BA11" s="3">
+      <c r="AZ11" s="3">
         <v>46094.943298610997</v>
       </c>
-      <c r="BB11" s="2" t="s">
-        <v>105</v>
+      <c r="BA11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB11" s="1">
+        <v>1</v>
       </c>
       <c r="BC11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE11" s="1">
         <v>9</v>
       </c>
       <c r="BF11" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG11" s="1">
         <v>0</v>
       </c>
-      <c r="BH11" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="4">
+      <c r="BH11" s="4">
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>906</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F12" s="3">
         <v>46095.423402777997</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -3094,180 +2980,177 @@
       <c r="K12" s="1">
         <v>1</v>
       </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>153</v>
+      <c r="L12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="1">
+        <v>2</v>
       </c>
       <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>3</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1">
+        <v>101</v>
+      </c>
+      <c r="T12" s="1">
+        <v>3</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
         <v>2</v>
       </c>
-      <c r="Q12" s="1">
-        <v>1</v>
-      </c>
-      <c r="R12" s="1">
+      <c r="W12" s="1">
+        <v>4</v>
+      </c>
+      <c r="X12" s="1">
         <v>3</v>
       </c>
-      <c r="S12" s="1">
-        <v>1</v>
-      </c>
-      <c r="T12" s="1">
+      <c r="Y12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>99</v>
+      </c>
+      <c r="AH12" s="1">
         <v>101</v>
       </c>
-      <c r="U12" s="1">
+      <c r="AI12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="1">
         <v>3</v>
       </c>
-      <c r="V12" s="1">
-        <v>1</v>
-      </c>
-      <c r="W12" s="1">
+      <c r="AK12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="1">
         <v>2</v>
       </c>
-      <c r="X12" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>5</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>5</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>99</v>
-      </c>
-      <c r="AI12" s="1">
+      <c r="AM12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="1">
         <v>101</v>
       </c>
-      <c r="AJ12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AK12" s="1">
-        <v>3</v>
-      </c>
-      <c r="AL12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="1">
-        <v>101</v>
+      <c r="AO12" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="AP12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AQ12" s="2" t="s">
         <v>111</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS12" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>9</v>
       </c>
       <c r="AT12" s="1">
+        <v>6</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>68</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>4</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>135</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>26</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>248</v>
+      </c>
+      <c r="AZ12" s="3">
+        <v>46095.426273147998</v>
+      </c>
+      <c r="BA12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="1">
         <v>9</v>
-      </c>
-      <c r="AU12" s="1">
-        <v>6</v>
-      </c>
-      <c r="AV12" s="1">
-        <v>68</v>
-      </c>
-      <c r="AW12" s="1">
-        <v>4</v>
-      </c>
-      <c r="AX12" s="1">
-        <v>135</v>
-      </c>
-      <c r="AY12" s="1">
-        <v>26</v>
-      </c>
-      <c r="AZ12" s="1">
-        <v>248</v>
-      </c>
-      <c r="BA12" s="3">
-        <v>46095.426273147998</v>
-      </c>
-      <c r="BB12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BC12" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD12" s="1">
-        <v>0</v>
       </c>
       <c r="BE12" s="1">
         <v>9</v>
       </c>
       <c r="BF12" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG12" s="1">
         <v>0</v>
       </c>
-      <c r="BH12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="4">
+      <c r="BH12" s="4">
         <v>1.21</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>908</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13" s="3">
         <v>46095.513460647999</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>156</v>
+        <v>143</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3275,180 +3158,177 @@
       <c r="K13" s="1">
         <v>1</v>
       </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>158</v>
+      <c r="L13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
       </c>
       <c r="P13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="1">
+        <v>91</v>
+      </c>
+      <c r="R13" s="1">
+        <v>14</v>
+      </c>
+      <c r="S13" s="1">
+        <v>24</v>
+      </c>
+      <c r="T13" s="1">
+        <v>85</v>
+      </c>
+      <c r="U13" s="1">
+        <v>64</v>
+      </c>
+      <c r="V13" s="1">
+        <v>38</v>
+      </c>
+      <c r="W13" s="1">
+        <v>47</v>
+      </c>
+      <c r="X13" s="1">
+        <v>63</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>76</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>16</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>37</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>101</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>73</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="1">
         <v>2</v>
       </c>
-      <c r="R13" s="1">
-        <v>91</v>
-      </c>
-      <c r="S13" s="1">
-        <v>14</v>
-      </c>
-      <c r="T13" s="1">
-        <v>24</v>
-      </c>
-      <c r="U13" s="1">
-        <v>85</v>
-      </c>
-      <c r="V13" s="1">
-        <v>64</v>
-      </c>
-      <c r="W13" s="1">
-        <v>38</v>
-      </c>
-      <c r="X13" s="1">
-        <v>47</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>63</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="1">
-        <v>16</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>76</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="1">
-        <v>16</v>
-      </c>
-      <c r="AG13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH13" s="1">
-        <v>37</v>
-      </c>
-      <c r="AI13" s="1">
-        <v>101</v>
-      </c>
-      <c r="AJ13" s="1">
-        <v>73</v>
-      </c>
-      <c r="AK13" s="1">
-        <v>1</v>
-      </c>
       <c r="AL13" s="1">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="AM13" s="1">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="AN13" s="1">
-        <v>28</v>
-      </c>
-      <c r="AO13" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="AP13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR13" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AQ13" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS13" s="2" t="s">
-        <v>113</v>
+      <c r="AS13" s="1">
+        <v>19</v>
       </c>
       <c r="AT13" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AU13" s="1">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="AV13" s="1">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AW13" s="1">
-        <v>10</v>
+        <v>228</v>
       </c>
       <c r="AX13" s="1">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="AY13" s="1">
-        <v>40</v>
-      </c>
-      <c r="AZ13" s="1">
         <v>361</v>
       </c>
-      <c r="BA13" s="3">
+      <c r="AZ13" s="3">
         <v>46095.517650463</v>
       </c>
-      <c r="BB13" s="2" t="s">
-        <v>105</v>
+      <c r="BA13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB13" s="1">
+        <v>1</v>
       </c>
       <c r="BC13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD13" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE13" s="1">
         <v>9</v>
       </c>
       <c r="BF13" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG13" s="1">
         <v>0</v>
       </c>
-      <c r="BH13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="4">
+      <c r="BH13" s="4">
         <v>0.78</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>921</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F14" s="3">
         <v>46096.400810184998</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -3456,180 +3336,177 @@
       <c r="K14" s="1">
         <v>1</v>
       </c>
-      <c r="L14" s="1">
-        <v>1</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="N14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>163</v>
+      <c r="L14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
       </c>
       <c r="P14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="1">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="R14" s="1">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="S14" s="1">
+        <v>19</v>
+      </c>
+      <c r="T14" s="1">
+        <v>30</v>
+      </c>
+      <c r="U14" s="1">
+        <v>16</v>
+      </c>
+      <c r="V14" s="1">
         <v>101</v>
       </c>
-      <c r="T14" s="1">
-        <v>19</v>
-      </c>
-      <c r="U14" s="1">
-        <v>30</v>
-      </c>
-      <c r="V14" s="1">
-        <v>16</v>
-      </c>
       <c r="W14" s="1">
+        <v>1</v>
+      </c>
+      <c r="X14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="1">
         <v>101</v>
       </c>
-      <c r="X14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>1</v>
-      </c>
       <c r="AH14" s="1">
+        <v>94</v>
+      </c>
+      <c r="AI14" s="1">
         <v>101</v>
-      </c>
-      <c r="AI14" s="1">
-        <v>94</v>
       </c>
       <c r="AJ14" s="1">
         <v>101</v>
       </c>
       <c r="AK14" s="1">
+        <v>53</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="1">
         <v>101</v>
-      </c>
-      <c r="AL14" s="1">
-        <v>53</v>
-      </c>
-      <c r="AM14" s="1">
-        <v>1</v>
       </c>
       <c r="AN14" s="1">
         <v>101</v>
       </c>
-      <c r="AO14" s="1">
-        <v>101</v>
+      <c r="AO14" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="AP14" s="2" t="s">
         <v>111</v>
       </c>
       <c r="AQ14" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AR14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS14" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>11</v>
       </c>
       <c r="AT14" s="1">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="AU14" s="1">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="AV14" s="1">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="AW14" s="1">
-        <v>10</v>
+        <v>228</v>
       </c>
       <c r="AX14" s="1">
-        <v>228</v>
+        <v>46</v>
       </c>
       <c r="AY14" s="1">
-        <v>46</v>
-      </c>
-      <c r="AZ14" s="1">
         <v>424</v>
       </c>
-      <c r="BA14" s="3">
+      <c r="AZ14" s="3">
         <v>46096.406215278002</v>
       </c>
-      <c r="BB14" s="2" t="s">
-        <v>105</v>
+      <c r="BA14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB14" s="1">
+        <v>1</v>
       </c>
       <c r="BC14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD14" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE14" s="1">
         <v>9</v>
       </c>
       <c r="BF14" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG14" s="1">
         <v>0</v>
       </c>
-      <c r="BH14" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="4">
+      <c r="BH14" s="4">
         <v>0.64</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>935</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F15" s="3">
         <v>46096.888321758997</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>166</v>
+        <v>151</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
@@ -3637,180 +3514,177 @@
       <c r="K15" s="1">
         <v>1</v>
       </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="N15" s="1">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>168</v>
+      <c r="L15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1</v>
       </c>
       <c r="P15" s="1">
         <v>1</v>
       </c>
       <c r="Q15" s="1">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="R15" s="1">
+        <v>78</v>
+      </c>
+      <c r="S15" s="1">
+        <v>50</v>
+      </c>
+      <c r="T15" s="1">
+        <v>6</v>
+      </c>
+      <c r="U15" s="1">
+        <v>101</v>
+      </c>
+      <c r="V15" s="1">
+        <v>47</v>
+      </c>
+      <c r="W15" s="1">
+        <v>23</v>
+      </c>
+      <c r="X15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>7</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>60</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="1">
         <v>71</v>
       </c>
-      <c r="S15" s="1">
-        <v>78</v>
-      </c>
-      <c r="T15" s="1">
-        <v>50</v>
-      </c>
-      <c r="U15" s="1">
-        <v>6</v>
-      </c>
-      <c r="V15" s="1">
+      <c r="AJ15" s="1">
         <v>101</v>
       </c>
-      <c r="W15" s="1">
-        <v>47</v>
-      </c>
-      <c r="X15" s="1">
-        <v>23</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC15" s="1">
-        <v>7</v>
-      </c>
-      <c r="AD15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE15" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="1">
-        <v>3</v>
-      </c>
-      <c r="AH15" s="1">
-        <v>60</v>
-      </c>
-      <c r="AI15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AJ15" s="1">
+      <c r="AK15" s="1">
+        <v>40</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>101</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>13</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>5</v>
+      </c>
+      <c r="AU15" s="1">
         <v>71</v>
       </c>
-      <c r="AK15" s="1">
-        <v>101</v>
-      </c>
-      <c r="AL15" s="1">
-        <v>40</v>
-      </c>
-      <c r="AM15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO15" s="1">
-        <v>101</v>
-      </c>
-      <c r="AP15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AR15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS15" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT15" s="1">
-        <v>13</v>
-      </c>
-      <c r="AU15" s="1">
-        <v>5</v>
-      </c>
       <c r="AV15" s="1">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="AW15" s="1">
-        <v>36</v>
+        <v>306</v>
       </c>
       <c r="AX15" s="1">
-        <v>306</v>
+        <v>52</v>
       </c>
       <c r="AY15" s="1">
-        <v>52</v>
-      </c>
-      <c r="AZ15" s="1">
         <v>454</v>
       </c>
-      <c r="BA15" s="3">
+      <c r="AZ15" s="3">
         <v>46096.893912036998</v>
       </c>
-      <c r="BB15" s="2" t="s">
-        <v>105</v>
+      <c r="BA15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB15" s="1">
+        <v>1</v>
       </c>
       <c r="BC15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE15" s="1">
         <v>9</v>
       </c>
       <c r="BF15" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG15" s="1">
         <v>0</v>
       </c>
-      <c r="BH15" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI15" s="4">
+      <c r="BH15" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>948</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F16" s="3">
         <v>46097.738518519</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>171</v>
+        <v>155</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
@@ -3818,56 +3692,56 @@
       <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N16" s="1">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>173</v>
+      <c r="L16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2</v>
       </c>
       <c r="P16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="1">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="R16" s="1">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="S16" s="1">
         <v>63</v>
       </c>
       <c r="T16" s="1">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="U16" s="1">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="V16" s="1">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="W16" s="1">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X16" s="1">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Y16" s="1">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="1">
         <v>1</v>
       </c>
       <c r="AA16" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AB16" s="1">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC16" s="1">
         <v>1</v>
@@ -3882,116 +3756,113 @@
         <v>1</v>
       </c>
       <c r="AG16" s="1">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="AH16" s="1">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="AI16" s="1">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="AJ16" s="1">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="AK16" s="1">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AL16" s="1">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="AM16" s="1">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="AN16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="1">
         <v>101</v>
       </c>
+      <c r="AO16" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="AP16" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AQ16" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS16" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AS16" s="1">
+        <v>3</v>
       </c>
       <c r="AT16" s="1">
         <v>3</v>
       </c>
       <c r="AU16" s="1">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AV16" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AW16" s="1">
-        <v>2</v>
+        <v>229</v>
       </c>
       <c r="AX16" s="1">
-        <v>229</v>
+        <v>31</v>
       </c>
       <c r="AY16" s="1">
-        <v>31</v>
-      </c>
-      <c r="AZ16" s="1">
         <v>293</v>
       </c>
-      <c r="BA16" s="3">
+      <c r="AZ16" s="3">
         <v>46097.741909721997</v>
       </c>
-      <c r="BB16" s="2" t="s">
-        <v>105</v>
+      <c r="BA16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB16" s="1">
+        <v>1</v>
       </c>
       <c r="BC16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD16" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE16" s="1">
         <v>9</v>
       </c>
       <c r="BF16" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG16" s="1">
         <v>0</v>
       </c>
-      <c r="BH16" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="4">
+      <c r="BH16" s="4">
         <v>2.14</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>959</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F17" s="3">
         <v>46097.774780093001</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>171</v>
+        <v>155</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
@@ -3999,180 +3870,177 @@
       <c r="K17" s="1">
         <v>1</v>
       </c>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N17" s="1">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>173</v>
+      <c r="L17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O17" s="1">
+        <v>2</v>
       </c>
       <c r="P17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="1">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="R17" s="1">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="S17" s="1">
+        <v>81</v>
+      </c>
+      <c r="T17" s="1">
+        <v>1</v>
+      </c>
+      <c r="U17" s="1">
+        <v>74</v>
+      </c>
+      <c r="V17" s="1">
+        <v>70</v>
+      </c>
+      <c r="W17" s="1">
+        <v>1</v>
+      </c>
+      <c r="X17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="1">
         <v>101</v>
       </c>
-      <c r="T17" s="1">
-        <v>81</v>
-      </c>
-      <c r="U17" s="1">
-        <v>1</v>
-      </c>
-      <c r="V17" s="1">
-        <v>74</v>
-      </c>
-      <c r="W17" s="1">
-        <v>70</v>
-      </c>
-      <c r="X17" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="1">
-        <v>1</v>
-      </c>
       <c r="AH17" s="1">
+        <v>26</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>84</v>
+      </c>
+      <c r="AJ17" s="1">
         <v>101</v>
       </c>
-      <c r="AI17" s="1">
-        <v>26</v>
-      </c>
-      <c r="AJ17" s="1">
-        <v>84</v>
-      </c>
       <c r="AK17" s="1">
+        <v>18</v>
+      </c>
+      <c r="AL17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="1">
         <v>101</v>
       </c>
-      <c r="AL17" s="1">
-        <v>18</v>
-      </c>
-      <c r="AM17" s="1">
-        <v>1</v>
-      </c>
       <c r="AN17" s="1">
-        <v>101</v>
-      </c>
-      <c r="AO17" s="1">
         <v>71</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="AP17" s="2" t="s">
         <v>111</v>
       </c>
       <c r="AQ17" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AR17" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS17" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="AS17" s="1">
+        <v>10</v>
       </c>
       <c r="AT17" s="1">
+        <v>9</v>
+      </c>
+      <c r="AU17" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV17" s="1">
         <v>10</v>
       </c>
-      <c r="AU17" s="1">
+      <c r="AW17" s="1">
+        <v>155</v>
+      </c>
+      <c r="AX17" s="1">
+        <v>32</v>
+      </c>
+      <c r="AY17" s="1">
+        <v>251</v>
+      </c>
+      <c r="AZ17" s="3">
+        <v>46097.777696759003</v>
+      </c>
+      <c r="BA17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC17" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD17" s="1">
         <v>9</v>
-      </c>
-      <c r="AV17" s="1">
-        <v>35</v>
-      </c>
-      <c r="AW17" s="1">
-        <v>10</v>
-      </c>
-      <c r="AX17" s="1">
-        <v>155</v>
-      </c>
-      <c r="AY17" s="1">
-        <v>32</v>
-      </c>
-      <c r="AZ17" s="1">
-        <v>251</v>
-      </c>
-      <c r="BA17" s="3">
-        <v>46097.777696759003</v>
-      </c>
-      <c r="BB17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BC17" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="1">
-        <v>0</v>
       </c>
       <c r="BE17" s="1">
         <v>9</v>
       </c>
       <c r="BF17" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG17" s="1">
         <v>0</v>
       </c>
-      <c r="BH17" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI17" s="4">
+      <c r="BH17" s="4">
         <v>1.06</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>960</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="3">
         <v>46097.862488425999</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>171</v>
+        <v>155</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
@@ -4180,62 +4048,62 @@
       <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>106</v>
+      <c r="L18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1</v>
       </c>
       <c r="P18" s="1">
         <v>1</v>
       </c>
       <c r="Q18" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R18" s="1">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="S18" s="1">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="T18" s="1">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="U18" s="1">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="V18" s="1">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="W18" s="1">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="X18" s="1">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="Y18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="1">
         <v>89</v>
       </c>
-      <c r="Z18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="1">
-        <v>9</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>1</v>
-      </c>
       <c r="AD18" s="1">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="AE18" s="1">
         <v>1</v>
@@ -4244,116 +4112,113 @@
         <v>1</v>
       </c>
       <c r="AG18" s="1">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="AH18" s="1">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="AI18" s="1">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="AJ18" s="1">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AK18" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AL18" s="1">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="AM18" s="1">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="AN18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="1">
         <v>58</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="AP18" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AQ18" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AR18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS18" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AS18" s="1">
+        <v>4</v>
       </c>
       <c r="AT18" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU18" s="1">
+        <v>23</v>
+      </c>
+      <c r="AV18" s="1">
         <v>2</v>
       </c>
-      <c r="AV18" s="1">
-        <v>23</v>
-      </c>
       <c r="AW18" s="1">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="AX18" s="1">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="AY18" s="1">
-        <v>22</v>
-      </c>
-      <c r="AZ18" s="1">
         <v>197</v>
       </c>
-      <c r="BA18" s="3">
+      <c r="AZ18" s="3">
         <v>46097.864768519001</v>
       </c>
-      <c r="BB18" s="2" t="s">
-        <v>105</v>
+      <c r="BA18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB18" s="1">
+        <v>1</v>
       </c>
       <c r="BC18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD18" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE18" s="1">
         <v>9</v>
       </c>
       <c r="BF18" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG18" s="1">
         <v>0</v>
       </c>
-      <c r="BH18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="4">
+      <c r="BH18" s="4">
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>961</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F19" s="3">
         <v>46097.869212963</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>171</v>
+        <v>155</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
       </c>
       <c r="J19" s="1">
         <v>1</v>
@@ -4361,180 +4226,177 @@
       <c r="K19" s="1">
         <v>1</v>
       </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="N19" s="1">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>183</v>
+      <c r="L19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O19" s="1">
+        <v>2</v>
       </c>
       <c r="P19" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="1">
         <v>2</v>
       </c>
-      <c r="Q19" s="1">
-        <v>1</v>
-      </c>
       <c r="R19" s="1">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="S19" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="T19" s="1">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="U19" s="1">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="V19" s="1">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="W19" s="1">
         <v>56</v>
       </c>
       <c r="X19" s="1">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Y19" s="1">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA19" s="1">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AB19" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AD19" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>81</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>38</v>
+      </c>
+      <c r="AH19" s="1">
         <v>15</v>
       </c>
-      <c r="AE19" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF19" s="1">
-        <v>81</v>
-      </c>
-      <c r="AG19" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="1">
-        <v>38</v>
-      </c>
       <c r="AI19" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ19" s="1">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="AK19" s="1">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AL19" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AM19" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AN19" s="1">
         <v>1</v>
       </c>
-      <c r="AO19" s="1">
-        <v>1</v>
+      <c r="AO19" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="AP19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AQ19" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS19" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AS19" s="1">
+        <v>10</v>
       </c>
       <c r="AT19" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AU19" s="1">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="AV19" s="1">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="AW19" s="1">
-        <v>13</v>
+        <v>310</v>
       </c>
       <c r="AX19" s="1">
-        <v>310</v>
+        <v>39</v>
       </c>
       <c r="AY19" s="1">
-        <v>39</v>
-      </c>
-      <c r="AZ19" s="1">
         <v>458</v>
       </c>
-      <c r="BA19" s="3">
+      <c r="AZ19" s="3">
         <v>46097.874513889001</v>
       </c>
-      <c r="BB19" s="2" t="s">
-        <v>105</v>
+      <c r="BA19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB19" s="1">
+        <v>1</v>
       </c>
       <c r="BC19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD19" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE19" s="1">
         <v>9</v>
       </c>
       <c r="BF19" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG19" s="1">
         <v>0</v>
       </c>
-      <c r="BH19" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI19" s="4">
+      <c r="BH19" s="4">
         <v>0.72</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>981</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="3">
         <v>46098.768125000002</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>186</v>
+        <v>166</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
       </c>
       <c r="J20" s="1">
         <v>1</v>
@@ -4542,180 +4404,177 @@
       <c r="K20" s="1">
         <v>1</v>
       </c>
-      <c r="L20" s="1">
-        <v>1</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N20" s="1">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>188</v>
+      <c r="L20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="M20" s="1">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1</v>
       </c>
       <c r="P20" s="1">
         <v>1</v>
       </c>
       <c r="Q20" s="1">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="R20" s="1">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="S20" s="1">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="T20" s="1">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="U20" s="1">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="V20" s="1">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="W20" s="1">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="X20" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y20" s="1">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="Z20" s="1">
         <v>2</v>
       </c>
       <c r="AA20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB20" s="1">
+        <v>53</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="1">
         <v>3</v>
       </c>
-      <c r="AC20" s="1">
-        <v>53</v>
-      </c>
-      <c r="AD20" s="1">
+      <c r="AF20" s="1">
+        <v>49</v>
+      </c>
+      <c r="AG20" s="1">
+        <v>101</v>
+      </c>
+      <c r="AH20" s="1">
+        <v>66</v>
+      </c>
+      <c r="AI20" s="1">
+        <v>99</v>
+      </c>
+      <c r="AJ20" s="1">
+        <v>20</v>
+      </c>
+      <c r="AK20" s="1">
         <v>5</v>
       </c>
-      <c r="AE20" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="1">
-        <v>3</v>
-      </c>
-      <c r="AG20" s="1">
-        <v>49</v>
-      </c>
-      <c r="AH20" s="1">
-        <v>101</v>
-      </c>
-      <c r="AI20" s="1">
-        <v>66</v>
-      </c>
-      <c r="AJ20" s="1">
-        <v>99</v>
-      </c>
-      <c r="AK20" s="1">
-        <v>20</v>
-      </c>
       <c r="AL20" s="1">
+        <v>97</v>
+      </c>
+      <c r="AM20" s="1">
+        <v>36</v>
+      </c>
+      <c r="AN20" s="1">
         <v>5</v>
       </c>
-      <c r="AM20" s="1">
-        <v>97</v>
-      </c>
-      <c r="AN20" s="1">
-        <v>36</v>
-      </c>
-      <c r="AO20" s="1">
-        <v>5</v>
+      <c r="AO20" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="AP20" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ20" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AR20" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS20" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
+      </c>
+      <c r="AS20" s="1">
+        <v>20</v>
       </c>
       <c r="AT20" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU20" s="1">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="AV20" s="1">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="AW20" s="1">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="AX20" s="1">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="AY20" s="1">
-        <v>53</v>
-      </c>
-      <c r="AZ20" s="1">
         <v>366</v>
       </c>
-      <c r="BA20" s="3">
+      <c r="AZ20" s="3">
         <v>46098.772361110998</v>
       </c>
-      <c r="BB20" s="2" t="s">
-        <v>105</v>
+      <c r="BA20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB20" s="1">
+        <v>1</v>
       </c>
       <c r="BC20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD20" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE20" s="1">
         <v>9</v>
       </c>
       <c r="BF20" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG20" s="1">
         <v>0</v>
       </c>
-      <c r="BH20" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI20" s="4">
+      <c r="BH20" s="4">
         <v>0.64</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>997</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F21" s="3">
         <v>46099.901481481</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>191</v>
+        <v>170</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
       </c>
       <c r="J21" s="1">
         <v>1</v>
@@ -4723,180 +4582,177 @@
       <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="N21" s="1">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>173</v>
+      <c r="L21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O21" s="1">
+        <v>2</v>
       </c>
       <c r="P21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="1">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="R21" s="1">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="S21" s="1">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="T21" s="1">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="U21" s="1">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="V21" s="1">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="W21" s="1">
+        <v>92</v>
+      </c>
+      <c r="X21" s="1">
+        <v>73</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>28</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>14</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>29</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>35</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>11</v>
+      </c>
+      <c r="AF21" s="1">
+        <v>32</v>
+      </c>
+      <c r="AG21" s="1">
         <v>90</v>
       </c>
-      <c r="X21" s="1">
-        <v>92</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>73</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="1">
+      <c r="AH21" s="1">
+        <v>51</v>
+      </c>
+      <c r="AI21" s="1">
         <v>28</v>
       </c>
-      <c r="AB21" s="1">
-        <v>14</v>
-      </c>
-      <c r="AC21" s="1">
-        <v>29</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE21" s="1">
-        <v>35</v>
-      </c>
-      <c r="AF21" s="1">
-        <v>11</v>
-      </c>
-      <c r="AG21" s="1">
-        <v>32</v>
-      </c>
-      <c r="AH21" s="1">
-        <v>90</v>
-      </c>
-      <c r="AI21" s="1">
-        <v>51</v>
-      </c>
       <c r="AJ21" s="1">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AK21" s="1">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AL21" s="1">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="AM21" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AN21" s="1">
-        <v>20</v>
-      </c>
-      <c r="AO21" s="1">
         <v>17</v>
       </c>
+      <c r="AO21" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="AP21" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AQ21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AR21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS21" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="AS21" s="1">
+        <v>5</v>
       </c>
       <c r="AT21" s="1">
         <v>5</v>
       </c>
       <c r="AU21" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AV21" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AW21" s="1">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="AX21" s="1">
-        <v>226</v>
+        <v>35</v>
       </c>
       <c r="AY21" s="1">
-        <v>35</v>
-      </c>
-      <c r="AZ21" s="1">
         <v>299</v>
       </c>
-      <c r="BA21" s="3">
+      <c r="AZ21" s="3">
         <v>46099.904942130001</v>
       </c>
-      <c r="BB21" s="2" t="s">
-        <v>105</v>
+      <c r="BA21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB21" s="1">
+        <v>1</v>
       </c>
       <c r="BC21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD21" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE21" s="1">
         <v>9</v>
       </c>
       <c r="BF21" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG21" s="1">
         <v>0</v>
       </c>
-      <c r="BH21" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI21" s="4">
+      <c r="BH21" s="4">
         <v>1.38</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>998</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F22" s="3">
         <v>46099.926400463002</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>191</v>
+        <v>170</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
       </c>
       <c r="J22" s="1">
         <v>1</v>
@@ -4904,47 +4760,47 @@
       <c r="K22" s="1">
         <v>1</v>
       </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="N22" s="1">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>106</v>
+      <c r="L22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O22" s="1">
+        <v>2</v>
       </c>
       <c r="P22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="1">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="R22" s="1">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="S22" s="1">
         <v>1</v>
       </c>
       <c r="T22" s="1">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="U22" s="1">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="V22" s="1">
+        <v>20</v>
+      </c>
+      <c r="W22" s="1">
+        <v>22</v>
+      </c>
+      <c r="X22" s="1">
         <v>78</v>
       </c>
-      <c r="W22" s="1">
-        <v>20</v>
-      </c>
-      <c r="X22" s="1">
-        <v>22</v>
-      </c>
       <c r="Y22" s="1">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="1">
         <v>1</v>
@@ -4968,297 +4824,291 @@
         <v>1</v>
       </c>
       <c r="AG22" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AH22" s="1">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="AI22" s="1">
         <v>76</v>
       </c>
       <c r="AJ22" s="1">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="AK22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="1">
+        <v>81</v>
+      </c>
+      <c r="AM22" s="1">
         <v>101</v>
       </c>
-      <c r="AL22" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM22" s="1">
-        <v>81</v>
-      </c>
       <c r="AN22" s="1">
-        <v>101</v>
-      </c>
-      <c r="AO22" s="1">
         <v>23</v>
       </c>
+      <c r="AO22" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="AP22" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AQ22" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AR22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS22" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AS22" s="1">
+        <v>2</v>
       </c>
       <c r="AT22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU22" s="1">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="AV22" s="1">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="AW22" s="1">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="AX22" s="1">
-        <v>186</v>
+        <v>34</v>
       </c>
       <c r="AY22" s="1">
-        <v>34</v>
-      </c>
-      <c r="AZ22" s="1">
         <v>281</v>
       </c>
-      <c r="BA22" s="3">
+      <c r="AZ22" s="3">
         <v>46099.929652778002</v>
       </c>
-      <c r="BB22" s="2" t="s">
-        <v>105</v>
+      <c r="BA22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB22" s="1">
+        <v>1</v>
       </c>
       <c r="BC22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD22" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE22" s="1">
         <v>9</v>
       </c>
       <c r="BF22" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG22" s="1">
         <v>0</v>
       </c>
-      <c r="BH22" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI22" s="4">
+      <c r="BH22" s="4">
         <v>1.72</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1009</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F23" s="3">
         <v>46099.975856481004</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M23" s="1">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O23" s="1">
+        <v>2</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>89</v>
+      </c>
+      <c r="R23" s="1">
+        <v>41</v>
+      </c>
+      <c r="S23" s="1">
+        <v>92</v>
+      </c>
+      <c r="T23" s="1">
+        <v>90</v>
+      </c>
+      <c r="U23" s="1">
+        <v>11</v>
+      </c>
+      <c r="V23" s="1">
+        <v>33</v>
+      </c>
+      <c r="W23" s="1">
+        <v>39</v>
+      </c>
+      <c r="X23" s="1">
+        <v>54</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>71</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>11</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>6</v>
+      </c>
+      <c r="AF23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>77</v>
+      </c>
+      <c r="AH23" s="1">
+        <v>80</v>
+      </c>
+      <c r="AI23" s="1">
+        <v>24</v>
+      </c>
+      <c r="AJ23" s="1">
+        <v>42</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>78</v>
+      </c>
+      <c r="AL23" s="1">
+        <v>74</v>
+      </c>
+      <c r="AM23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AR23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AS23" s="1">
+        <v>6</v>
+      </c>
+      <c r="AT23" s="1">
+        <v>15</v>
+      </c>
+      <c r="AU23" s="1">
+        <v>27</v>
+      </c>
+      <c r="AV23" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW23" s="1">
         <v>197</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="N23" s="1">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="P23" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>1</v>
-      </c>
-      <c r="R23" s="1">
-        <v>89</v>
-      </c>
-      <c r="S23" s="1">
-        <v>41</v>
-      </c>
-      <c r="T23" s="1">
-        <v>92</v>
-      </c>
-      <c r="U23" s="1">
-        <v>90</v>
-      </c>
-      <c r="V23" s="1">
-        <v>11</v>
-      </c>
-      <c r="W23" s="1">
-        <v>33</v>
-      </c>
-      <c r="X23" s="1">
-        <v>39</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>54</v>
-      </c>
-      <c r="Z23" s="1">
-        <v>71</v>
-      </c>
-      <c r="AA23" s="1">
-        <v>11</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>12</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="1">
-        <v>6</v>
-      </c>
-      <c r="AG23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH23" s="1">
-        <v>77</v>
-      </c>
-      <c r="AI23" s="1">
-        <v>80</v>
-      </c>
-      <c r="AJ23" s="1">
+      <c r="AX23" s="1">
         <v>24</v>
       </c>
-      <c r="AK23" s="1">
-        <v>42</v>
-      </c>
-      <c r="AL23" s="1">
-        <v>78</v>
-      </c>
-      <c r="AM23" s="1">
-        <v>74</v>
-      </c>
-      <c r="AN23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT23" s="1">
-        <v>6</v>
-      </c>
-      <c r="AU23" s="1">
-        <v>15</v>
-      </c>
-      <c r="AV23" s="1">
-        <v>27</v>
-      </c>
-      <c r="AW23" s="1">
-        <v>5</v>
-      </c>
-      <c r="AX23" s="1">
-        <v>197</v>
-      </c>
       <c r="AY23" s="1">
-        <v>24</v>
-      </c>
-      <c r="AZ23" s="1">
         <v>274</v>
       </c>
-      <c r="BA23" s="3">
+      <c r="AZ23" s="3">
         <v>46099.979027777998</v>
       </c>
-      <c r="BB23" s="2" t="s">
-        <v>105</v>
+      <c r="BA23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB23" s="1">
+        <v>1</v>
       </c>
       <c r="BC23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD23" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE23" s="1">
         <v>9</v>
       </c>
       <c r="BF23" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG23" s="1">
         <v>0</v>
       </c>
-      <c r="BH23" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI23" s="4">
+      <c r="BH23" s="4">
         <v>1.23</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1030</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F24" s="3">
         <v>46102.683194443998</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
       </c>
       <c r="J24" s="1">
         <v>1</v>
@@ -5266,180 +5116,177 @@
       <c r="K24" s="1">
         <v>1</v>
       </c>
-      <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="N24" s="1">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>203</v>
+      <c r="L24" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M24" s="1">
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="O24" s="1">
+        <v>2</v>
       </c>
       <c r="P24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="1">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="R24" s="1">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="S24" s="1">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1">
+        <v>1</v>
+      </c>
+      <c r="U24" s="1">
+        <v>79</v>
+      </c>
+      <c r="V24" s="1">
+        <v>29</v>
+      </c>
+      <c r="W24" s="1">
+        <v>18</v>
+      </c>
+      <c r="X24" s="1">
+        <v>20</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="1">
         <v>101</v>
       </c>
-      <c r="T24" s="1">
-        <v>1</v>
-      </c>
-      <c r="U24" s="1">
-        <v>1</v>
-      </c>
-      <c r="V24" s="1">
-        <v>79</v>
-      </c>
-      <c r="W24" s="1">
-        <v>29</v>
-      </c>
-      <c r="X24" s="1">
-        <v>18</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>20</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE24" s="1">
-        <v>4</v>
-      </c>
-      <c r="AF24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="1">
-        <v>1</v>
-      </c>
       <c r="AH24" s="1">
+        <v>72</v>
+      </c>
+      <c r="AI24" s="1">
         <v>101</v>
-      </c>
-      <c r="AI24" s="1">
-        <v>72</v>
       </c>
       <c r="AJ24" s="1">
         <v>101</v>
       </c>
       <c r="AK24" s="1">
+        <v>17</v>
+      </c>
+      <c r="AL24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM24" s="1">
+        <v>97</v>
+      </c>
+      <c r="AN24" s="1">
         <v>101</v>
       </c>
-      <c r="AL24" s="1">
-        <v>17</v>
-      </c>
-      <c r="AM24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN24" s="1">
-        <v>97</v>
-      </c>
-      <c r="AO24" s="1">
-        <v>101</v>
+      <c r="AO24" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="AP24" s="2" t="s">
         <v>111</v>
       </c>
       <c r="AQ24" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AR24" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AS24" s="2" t="s">
-        <v>112</v>
+      <c r="AS24" s="1">
+        <v>22</v>
       </c>
       <c r="AT24" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AU24" s="1">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="AV24" s="1">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="AW24" s="1">
+        <v>232</v>
+      </c>
+      <c r="AX24" s="1">
+        <v>51</v>
+      </c>
+      <c r="AY24" s="1">
+        <v>401</v>
+      </c>
+      <c r="AZ24" s="3">
+        <v>46102.687835648001</v>
+      </c>
+      <c r="BA24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB24" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC24" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD24" s="1">
         <v>9</v>
-      </c>
-      <c r="AX24" s="1">
-        <v>232</v>
-      </c>
-      <c r="AY24" s="1">
-        <v>51</v>
-      </c>
-      <c r="AZ24" s="1">
-        <v>401</v>
-      </c>
-      <c r="BA24" s="3">
-        <v>46102.687835648001</v>
-      </c>
-      <c r="BB24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BC24" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD24" s="1">
-        <v>0</v>
       </c>
       <c r="BE24" s="1">
         <v>9</v>
       </c>
       <c r="BF24" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG24" s="1">
         <v>0</v>
       </c>
-      <c r="BH24" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI24" s="4">
+      <c r="BH24" s="4">
         <v>0.69</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1145</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F25" s="3">
         <v>46104.837129630003</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>206</v>
+        <v>181</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
@@ -5447,17 +5294,17 @@
       <c r="K25" s="1">
         <v>1</v>
       </c>
-      <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="N25" s="1">
-        <v>1</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>127</v>
+      <c r="L25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M25" s="1">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1</v>
       </c>
       <c r="P25" s="1">
         <v>1</v>
@@ -5466,162 +5313,159 @@
         <v>1</v>
       </c>
       <c r="R25" s="1">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="S25" s="1">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="T25" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="U25" s="1">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="V25" s="1">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="W25" s="1">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="X25" s="1">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="Y25" s="1">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AA25" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AB25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="1">
         <v>2</v>
       </c>
-      <c r="AD25" s="1">
-        <v>1</v>
-      </c>
       <c r="AE25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="1">
         <v>2</v>
       </c>
-      <c r="AF25" s="1">
-        <v>1</v>
-      </c>
       <c r="AG25" s="1">
+        <v>101</v>
+      </c>
+      <c r="AH25" s="1">
+        <v>52</v>
+      </c>
+      <c r="AI25" s="1">
+        <v>100</v>
+      </c>
+      <c r="AJ25" s="1">
+        <v>101</v>
+      </c>
+      <c r="AK25" s="1">
+        <v>84</v>
+      </c>
+      <c r="AL25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM25" s="1">
+        <v>60</v>
+      </c>
+      <c r="AN25" s="1">
+        <v>27</v>
+      </c>
+      <c r="AO25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU25" s="1">
+        <v>15</v>
+      </c>
+      <c r="AV25" s="1">
         <v>2</v>
       </c>
-      <c r="AH25" s="1">
-        <v>101</v>
-      </c>
-      <c r="AI25" s="1">
-        <v>52</v>
-      </c>
-      <c r="AJ25" s="1">
-        <v>100</v>
-      </c>
-      <c r="AK25" s="1">
-        <v>101</v>
-      </c>
-      <c r="AL25" s="1">
-        <v>84</v>
-      </c>
-      <c r="AM25" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN25" s="1">
-        <v>60</v>
-      </c>
-      <c r="AO25" s="1">
-        <v>27</v>
-      </c>
-      <c r="AP25" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AQ25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AR25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AT25" s="1">
-        <v>1</v>
-      </c>
-      <c r="AU25" s="1">
-        <v>1</v>
-      </c>
-      <c r="AV25" s="1">
-        <v>15</v>
-      </c>
       <c r="AW25" s="1">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="AX25" s="1">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="AY25" s="1">
-        <v>23</v>
-      </c>
-      <c r="AZ25" s="1">
         <v>242</v>
       </c>
-      <c r="BA25" s="3"/>
-      <c r="BB25" s="3">
+      <c r="AZ25" s="3"/>
+      <c r="BA25" s="3">
         <v>46104.839942129998</v>
       </c>
-      <c r="BC25" s="2" t="s">
-        <v>105</v>
+      <c r="BB25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC25" s="1">
+        <v>1</v>
       </c>
       <c r="BD25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE25" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF25" s="1">
         <v>9</v>
       </c>
       <c r="BG25" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BH25" s="1">
         <v>0</v>
       </c>
-      <c r="BI25" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ25" s="4">
+      <c r="BI25" s="4">
         <v>2.42</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1225</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F26" s="3">
         <v>46105.342210647999</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>210</v>
+        <v>184</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
       </c>
       <c r="J26" s="1">
         <v>1</v>
@@ -5629,181 +5473,178 @@
       <c r="K26" s="1">
         <v>1</v>
       </c>
-      <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="N26" s="1">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>127</v>
+      <c r="L26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M26" s="1">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="O26" s="1">
+        <v>2</v>
       </c>
       <c r="P26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="1">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="R26" s="1">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="S26" s="1">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="T26" s="1">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="U26" s="1">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="V26" s="1">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="W26" s="1">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="X26" s="1">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="Y26" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="1">
         <v>1</v>
       </c>
       <c r="AA26" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AB26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="1">
+        <v>61</v>
+      </c>
+      <c r="AH26" s="1">
+        <v>83</v>
+      </c>
+      <c r="AI26" s="1">
+        <v>77</v>
+      </c>
+      <c r="AJ26" s="1">
+        <v>97</v>
+      </c>
+      <c r="AK26" s="1">
+        <v>16</v>
+      </c>
+      <c r="AL26" s="1">
+        <v>81</v>
+      </c>
+      <c r="AM26" s="1">
         <v>11</v>
       </c>
-      <c r="AC26" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH26" s="1">
-        <v>61</v>
-      </c>
-      <c r="AI26" s="1">
-        <v>83</v>
-      </c>
-      <c r="AJ26" s="1">
-        <v>77</v>
-      </c>
-      <c r="AK26" s="1">
-        <v>97</v>
-      </c>
-      <c r="AL26" s="1">
-        <v>16</v>
-      </c>
-      <c r="AM26" s="1">
+      <c r="AN26" s="1">
         <v>81</v>
       </c>
-      <c r="AN26" s="1">
-        <v>11</v>
-      </c>
-      <c r="AO26" s="1">
-        <v>81</v>
+      <c r="AO26" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="AP26" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ26" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AR26" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AS26" s="2" t="s">
-        <v>112</v>
+      <c r="AS26" s="1">
+        <v>2</v>
       </c>
       <c r="AT26" s="1">
         <v>2</v>
       </c>
       <c r="AU26" s="1">
+        <v>26</v>
+      </c>
+      <c r="AV26" s="1">
         <v>2</v>
       </c>
-      <c r="AV26" s="1">
-        <v>26</v>
-      </c>
       <c r="AW26" s="1">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="AX26" s="1">
-        <v>232</v>
+        <v>41</v>
       </c>
       <c r="AY26" s="1">
-        <v>41</v>
-      </c>
-      <c r="AZ26" s="1">
         <v>305</v>
       </c>
-      <c r="BA26" s="3"/>
-      <c r="BB26" s="3">
+      <c r="AZ26" s="3"/>
+      <c r="BA26" s="3">
         <v>46105.345740741002</v>
       </c>
-      <c r="BC26" s="2" t="s">
-        <v>105</v>
+      <c r="BB26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC26" s="1">
+        <v>1</v>
       </c>
       <c r="BD26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE26" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF26" s="1">
         <v>9</v>
       </c>
       <c r="BG26" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BH26" s="1">
         <v>0</v>
       </c>
-      <c r="BI26" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ26" s="4">
+      <c r="BI26" s="4">
         <v>2.08</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1499</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F27" s="3">
         <v>46118.571724537003</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>214</v>
+        <v>187</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
       </c>
       <c r="J27" s="1">
         <v>1</v>
@@ -5811,155 +5652,152 @@
       <c r="K27" s="1">
         <v>1</v>
       </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="N27" s="1">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>216</v>
+      <c r="L27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1</v>
       </c>
       <c r="P27" s="1">
         <v>1</v>
       </c>
       <c r="Q27" s="1">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="R27" s="1">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="S27" s="1">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="T27" s="1">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="U27" s="1">
+        <v>50</v>
+      </c>
+      <c r="V27" s="1">
+        <v>51</v>
+      </c>
+      <c r="W27" s="1">
+        <v>77</v>
+      </c>
+      <c r="X27" s="1">
+        <v>68</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="1">
         <v>17</v>
       </c>
-      <c r="V27" s="1">
+      <c r="AA27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="1">
+        <v>22</v>
+      </c>
+      <c r="AC27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>29</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="1">
+        <v>23</v>
+      </c>
+      <c r="AG27" s="1">
+        <v>57</v>
+      </c>
+      <c r="AH27" s="1">
+        <v>55</v>
+      </c>
+      <c r="AI27" s="1">
         <v>50</v>
       </c>
-      <c r="W27" s="1">
-        <v>51</v>
-      </c>
-      <c r="X27" s="1">
-        <v>77</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>68</v>
-      </c>
-      <c r="Z27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="1">
-        <v>17</v>
-      </c>
-      <c r="AB27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="1">
-        <v>22</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE27" s="1">
-        <v>29</v>
-      </c>
-      <c r="AF27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="1">
-        <v>23</v>
-      </c>
-      <c r="AH27" s="1">
-        <v>57</v>
-      </c>
-      <c r="AI27" s="1">
-        <v>55</v>
-      </c>
       <c r="AJ27" s="1">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="AK27" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AL27" s="1">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AM27" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AN27" s="1">
-        <v>31</v>
-      </c>
-      <c r="AO27" s="1">
         <v>19</v>
       </c>
+      <c r="AO27" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="AP27" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AQ27" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AR27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS27" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="AS27" s="1">
+        <v>6</v>
       </c>
       <c r="AT27" s="1">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="AU27" s="1">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="AV27" s="1">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="AW27" s="1">
-        <v>13</v>
+        <v>349</v>
       </c>
       <c r="AX27" s="1">
-        <v>349</v>
+        <v>25</v>
       </c>
       <c r="AY27" s="1">
-        <v>25</v>
-      </c>
-      <c r="AZ27" s="1">
         <v>299</v>
       </c>
-      <c r="BA27" s="3"/>
-      <c r="BB27" s="3">
+      <c r="AZ27" s="3"/>
+      <c r="BA27" s="3">
         <v>46118.578287037002</v>
       </c>
-      <c r="BC27" s="2" t="s">
-        <v>105</v>
+      <c r="BB27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC27" s="1">
+        <v>1</v>
       </c>
       <c r="BD27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE27" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF27" s="1">
         <v>9</v>
       </c>
       <c r="BG27" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BH27" s="1">
         <v>0</v>
       </c>
-      <c r="BI27" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ27" s="4">
+      <c r="BI27" s="4">
         <v>0.85</v>
       </c>
     </row>

--- a/DAT/raw/data_BodyPerception_new.xlsx
+++ b/DAT/raw/data_BodyPerception_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/delphinehund/Desktop/Stage/Pilot_Study-SocBodPer/V2/code/DAT/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AB290B-19CF-1949-823E-F126F4C0DC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36477EA0-8FF6-6449-9403-5BFC0E77908A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11620" yWindow="2600" windowWidth="16380" windowHeight="16520" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -967,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI27"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3840,7 +3840,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>959</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>960</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>961</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>981</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>997</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>998</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1009</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1030</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1145</v>
       </c>
@@ -5414,36 +5414,35 @@
       <c r="AY25" s="1">
         <v>242</v>
       </c>
-      <c r="AZ25" s="3"/>
-      <c r="BA25" s="3">
+      <c r="AZ25" s="3">
         <v>46104.839942129998</v>
       </c>
-      <c r="BB25" s="2" t="s">
+      <c r="BA25" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="BB25" s="1">
+        <v>1</v>
+      </c>
       <c r="BC25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD25" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE25" s="1">
         <v>9</v>
       </c>
       <c r="BF25" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG25" s="1">
         <v>0</v>
       </c>
-      <c r="BH25" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI25" s="4">
+      <c r="BH25" s="4">
         <v>2.42</v>
       </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1225</v>
       </c>
@@ -5593,36 +5592,35 @@
       <c r="AY26" s="1">
         <v>305</v>
       </c>
-      <c r="AZ26" s="3"/>
-      <c r="BA26" s="3">
+      <c r="AZ26" s="3">
         <v>46105.345740741002</v>
       </c>
-      <c r="BB26" s="2" t="s">
+      <c r="BA26" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="BB26" s="1">
+        <v>1</v>
+      </c>
       <c r="BC26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD26" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE26" s="1">
         <v>9</v>
       </c>
       <c r="BF26" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG26" s="1">
         <v>0</v>
       </c>
-      <c r="BH26" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI26" s="4">
+      <c r="BH26" s="4">
         <v>2.08</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:60" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1499</v>
       </c>
@@ -5772,32 +5770,31 @@
       <c r="AY27" s="1">
         <v>299</v>
       </c>
-      <c r="AZ27" s="3"/>
-      <c r="BA27" s="3">
+      <c r="AZ27" s="3">
         <v>46118.578287037002</v>
       </c>
-      <c r="BB27" s="2" t="s">
+      <c r="BA27" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="BB27" s="1">
+        <v>1</v>
+      </c>
       <c r="BC27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD27" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE27" s="1">
         <v>9</v>
       </c>
       <c r="BF27" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG27" s="1">
         <v>0</v>
       </c>
-      <c r="BH27" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI27" s="4">
+      <c r="BH27" s="4">
         <v>0.85</v>
       </c>
     </row>
